--- a/docs/diff_map.xlsx
+++ b/docs/diff_map.xlsx
@@ -432,19 +432,19 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.86891310437455982</c:v>
+                  <c:v>0.8689131043745597</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.76634591660498397</c:v>
+                  <c:v>0.7058823529411764</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6658880094220041</c:v>
+                  <c:v>0.6133504266173363</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.59786370542100298</c:v>
+                  <c:v>0.597863705421003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.45817040933571068</c:v>
+                  <c:v>0.422021439120708</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -675,19 +675,19 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.80904494997656273</c:v>
+                  <c:v>0.8090449499765627</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.76634591660498397</c:v>
+                  <c:v>0.7058823529411765</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.65557648104589672</c:v>
+                  <c:v>0.6555764810458966</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.62000829376442235</c:v>
+                  <c:v>0.5710905529246325</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.50239835927178755</c:v>
+                  <c:v>0.4627598689735741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -912,13 +912,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.76634591660498397</c:v>
+                  <c:v>0.7058823529411764</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.54267864568626134</c:v>
+                  <c:v>0.5426786456862612</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.41587956415038935</c:v>
+                  <c:v>0.3830672793079491</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1422,21 +1422,12 @@
     </row>
     <row r="3" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="2">
-        <f t="shared" ref="B3:B4" si="0">(1/TAN(46*PI()/180))/(1/TAN(35*PI()/180))*0.325*(1+(A3-8)*0.0947)*2</f>
-        <v>0.10653932410387595</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="2">
-        <f t="shared" ref="D3:D8" si="1">(1/TAN(72*PI()/180))/(1/TAN(35*PI()/180))*0.325*(1+(A3-8)*0.0947)*2</f>
-        <v>3.5846667920113581E-2</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="2">
-        <f t="shared" ref="G3:G4" si="2">(1/TAN(38*PI()/180))/(1/TAN(35*PI()/180))*0.325*(1+(F3-8)*0.0947)*2</f>
-        <v>0.14120917623124007</v>
-      </c>
+      <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -1445,21 +1436,16 @@
     </row>
     <row r="4" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="12">
-        <f t="shared" si="0"/>
-        <v>0.10653932410387595</v>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>相对值以各图注明的参考组合为 100%；完整系数与模型等效百分比见 Samples。</t>
+        </is>
       </c>
       <c r="C4" s="12"/>
-      <c r="D4" s="12">
-        <f t="shared" si="1"/>
-        <v>3.5846667920113581E-2</v>
-      </c>
+      <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="12">
-        <f t="shared" si="2"/>
-        <v>0.14120917623124007</v>
-      </c>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -1499,18 +1485,12 @@
     </row>
     <row r="7" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="2">
-        <f t="shared" ref="B7:B8" si="3">(1/TAN(50*PI()/180))/(1/TAN(35*PI()/180))*0.325*(1+(A7-8)*0.0947)*2</f>
-        <v>9.2573414845066218E-2</v>
-      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2">
-        <f t="shared" ref="G7:G8" si="4">(1/TAN(44*PI()/180))/(1/TAN(35*PI()/180))*0.325*(1+(F7-8)*0.0947)*2</f>
-        <v>0.11424457092023524</v>
-      </c>
+      <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -1519,21 +1499,12 @@
     </row>
     <row r="8" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <f t="shared" si="3"/>
-        <v>9.2573414845066218E-2</v>
-      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="2">
-        <f t="shared" si="1"/>
-        <v>3.5846667920113581E-2</v>
-      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2">
-        <f t="shared" si="4"/>
-        <v>0.11424457092023524</v>
-      </c>
+      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1570,18 +1541,12 @@
     </row>
     <row r="11" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="2">
-        <f t="shared" ref="B11:B12" si="5">(1/TAN(60*PI()/180))/(1/TAN(35*PI()/180))*0.325*(1+(A11-8)*0.0947)*2</f>
-        <v>6.3695995081792453E-2</v>
-      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2">
-        <f t="shared" ref="G11:G12" si="6">(1/TAN(50*PI()/180))/(1/TAN(35*PI()/180))*0.325*(1+(F11-8)*0.0947)*2</f>
-        <v>9.2573414845066218E-2</v>
-      </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -1590,18 +1555,12 @@
     </row>
     <row r="12" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="2">
-        <f t="shared" si="5"/>
-        <v>6.3695995081792453E-2</v>
-      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2">
-        <f t="shared" si="6"/>
-        <v>9.2573414845066218E-2</v>
-      </c>
+      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1652,18 +1611,12 @@
     </row>
     <row r="16" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="2">
-        <f t="shared" ref="B16:B17" si="7">B3</f>
-        <v>0.10653932410387595</v>
-      </c>
+      <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2">
-        <f t="shared" ref="G16:G17" si="8">G3</f>
-        <v>0.14120917623124007</v>
-      </c>
+      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -1672,18 +1625,12 @@
     </row>
     <row r="17" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="B17" s="2">
-        <f t="shared" si="7"/>
-        <v>0.10653932410387595</v>
-      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="2">
-        <f t="shared" si="8"/>
-        <v>0.14120917623124007</v>
-      </c>
+      <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -1692,18 +1639,12 @@
     </row>
     <row r="18" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="2">
-        <f t="shared" ref="B18:B19" si="9">B7</f>
-        <v>9.2573414845066218E-2</v>
-      </c>
+      <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2">
-        <f t="shared" ref="G18:G19" si="10">G7</f>
-        <v>0.11424457092023524</v>
-      </c>
+      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -1712,18 +1653,12 @@
     </row>
     <row r="19" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="2">
-        <f t="shared" si="9"/>
-        <v>9.2573414845066218E-2</v>
-      </c>
+      <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="2">
-        <f t="shared" si="10"/>
-        <v>0.11424457092023524</v>
-      </c>
+      <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1732,18 +1667,12 @@
     </row>
     <row r="20" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="2">
-        <f t="shared" ref="B20:B21" si="11">B11</f>
-        <v>6.3695995081792453E-2</v>
-      </c>
+      <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2">
-        <f t="shared" ref="G20:G21" si="12">G11</f>
-        <v>9.2573414845066218E-2</v>
-      </c>
+      <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -1752,18 +1681,15 @@
     </row>
     <row r="21" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
-      <c r="B21" s="13">
-        <f t="shared" si="11"/>
-        <v>6.3695995081792453E-2</v>
+      <c r="B21" s="13" t="str">
+        <f>"Rear power："&amp;Samples!E12&amp;" = 100%"</f>
+        <v>Rear power：38° / 6+6 = 100%</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
-      <c r="G21" s="13">
-        <f t="shared" si="12"/>
-        <v>9.2573414845066218E-2</v>
-      </c>
+      <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
@@ -1772,18 +1698,12 @@
     </row>
     <row r="22" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
-      <c r="B22" s="2">
-        <f t="shared" ref="B22:B23" si="13">D3</f>
-        <v>3.5846667920113581E-2</v>
-      </c>
+      <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2">
-        <f t="shared" ref="G22:G23" si="14">H3</f>
-        <v>0</v>
-      </c>
+      <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -1792,18 +1712,12 @@
     </row>
     <row r="23" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
-      <c r="B23" s="2">
-        <f t="shared" si="13"/>
-        <v>3.5846667920113581E-2</v>
-      </c>
+      <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="2">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
+      <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -1812,10 +1726,7 @@
     </row>
     <row r="24" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
-      <c r="B24" s="2">
-        <f t="shared" ref="B24:B25" si="15">C3</f>
-        <v>0</v>
-      </c>
+      <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1829,10 +1740,7 @@
     </row>
     <row r="25" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
-      <c r="B25" s="2">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
+      <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -2409,7 +2317,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -2435,20 +2343,22 @@
         <v>13</v>
       </c>
       <c r="C9" s="5">
-        <v>0.32500000000000001</v>
+        <v>0.20189</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>15</v>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>锚点 / 原 Q6</t>
+        </is>
       </c>
       <c r="G9" s="4">
         <v>35</v>
       </c>
       <c r="H9" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -2461,7 +2371,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="5">
-        <v>9.4700000000000006E-2</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -2789,8 +2699,10 @@
     </row>
     <row r="28" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
-      <c r="B28" s="16" t="s">
-        <v>32</v>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>模型等效百分比 = c × 换算倍数；35°、4+4 的 c = 0.20189，对应 40.378%。</t>
+        </is>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -2869,8 +2781,10 @@
     </row>
     <row r="33" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
-      <c r="B33" s="12" t="s">
-        <v>37</v>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>FF 折中标定：保留 4+4；每侧增加一面，锚点系数增加 5/24。</t>
+        </is>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -3060,14 +2974,14 @@
       </c>
       <c r="F6" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C6*PI()/180)*Parameters!$C$9*(1+(D6-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.17813691443605995</v>
+        <v>0.19339553738080512</v>
       </c>
       <c r="G6" s="8">
         <f>F6*Parameters!$C$11</f>
-        <v>0.35627382887211989</v>
+        <v>0.38679107476161023</v>
       </c>
       <c r="H6" s="8">
-        <f t="shared" ref="H6:H11" si="1">G6/$G$6</f>
+        <f>G6/$G$6</f>
         <v>1</v>
       </c>
       <c r="I6" s="2"/>
@@ -3092,15 +3006,15 @@
       </c>
       <c r="F7" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C7*PI()/180)*Parameters!$C$9*(1+(D7-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.1547854993263422</v>
+        <v>0.16804391675774158</v>
       </c>
       <c r="G7" s="8">
         <f>F7*Parameters!$C$11</f>
-        <v>0.30957099865268439</v>
+        <v>0.33608783351548316</v>
       </c>
       <c r="H7" s="8">
-        <f t="shared" si="1"/>
-        <v>0.86891310437455982</v>
+        <f>G7/$G$6</f>
+        <v>0.8689131043745597</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -3128,11 +3042,11 @@
       </c>
       <c r="G8" s="8">
         <f>F8*Parameters!$C$11</f>
-        <v>0.27302899394937191</v>
+        <v>0.2730289939493719</v>
       </c>
       <c r="H8" s="8">
-        <f t="shared" si="1"/>
-        <v>0.76634591660498397</v>
+        <f>G8/$G$6</f>
+        <v>0.7058823529411764</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -3163,8 +3077,8 @@
         <v>0.23723847071681164</v>
       </c>
       <c r="H9" s="8">
-        <f t="shared" si="1"/>
-        <v>0.6658880094220041</v>
+        <f>G9/$G$6</f>
+        <v>0.6133504266173363</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -3188,15 +3102,15 @@
       </c>
       <c r="F10" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C10*PI()/180)*Parameters!$C$9*(1+(D10-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.10650159573700696</v>
+        <v>0.11562417259037425</v>
       </c>
       <c r="G10" s="8">
         <f>F10*Parameters!$C$11</f>
-        <v>0.21300319147401392</v>
+        <v>0.2312483451807485</v>
       </c>
       <c r="H10" s="8">
-        <f t="shared" si="1"/>
-        <v>0.59786370542100298</v>
+        <f>G10/$G$6</f>
+        <v>0.597863705421003</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -3220,15 +3134,15 @@
       </c>
       <c r="F11" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C11*PI()/180)*Parameters!$C$9*(1+(D11-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>8.1617063004970056E-2</v>
+        <v>0.08161706300497006</v>
       </c>
       <c r="G11" s="8">
         <f>F11*Parameters!$C$11</f>
-        <v>0.16323412600994011</v>
+        <v>0.1632341260099401</v>
       </c>
       <c r="H11" s="8">
-        <f t="shared" si="1"/>
-        <v>0.45817040933571068</v>
+        <f>G11/$G$6</f>
+        <v>0.422021439120708</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -3252,14 +3166,14 @@
       </c>
       <c r="F12" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C12*PI()/180)*Parameters!$C$9*(1+(D12-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.23610593699060067</v>
+        <v>0.25632999599016565</v>
       </c>
       <c r="G12" s="8">
         <f>F12*Parameters!$C$11</f>
-        <v>0.47221187398120135</v>
+        <v>0.5126599919803313</v>
       </c>
       <c r="H12" s="8">
-        <f t="shared" ref="H12:H17" si="2">G12/$G$12</f>
+        <f>G12/$G$12</f>
         <v>1</v>
       </c>
       <c r="I12" s="2"/>
@@ -3284,15 +3198,15 @@
       </c>
       <c r="F13" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C13*PI()/180)*Parameters!$C$9*(1+(D13-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.19102031598173</v>
+        <v>0.2073824887833561</v>
       </c>
       <c r="G13" s="8">
         <f>F13*Parameters!$C$11</f>
-        <v>0.38204063196346</v>
+        <v>0.4147649775667122</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="2"/>
-        <v>0.80904494997656273</v>
+        <f>G13/$G$12</f>
+        <v>0.8090449499765627</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -3320,11 +3234,11 @@
       </c>
       <c r="G14" s="8">
         <f>F14*Parameters!$C$11</f>
-        <v>0.36187764139788092</v>
+        <v>0.3618776413978809</v>
       </c>
       <c r="H14" s="8">
-        <f t="shared" si="2"/>
-        <v>0.76634591660498397</v>
+        <f>G14/$G$12</f>
+        <v>0.7058823529411765</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -3348,15 +3262,15 @@
       </c>
       <c r="F15" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C15*PI()/180)*Parameters!$C$9*(1+(D15-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.1547854993263422</v>
+        <v>0.16804391675774158</v>
       </c>
       <c r="G15" s="8">
         <f>F15*Parameters!$C$11</f>
-        <v>0.30957099865268439</v>
+        <v>0.33608783351548316</v>
       </c>
       <c r="H15" s="8">
-        <f t="shared" si="2"/>
-        <v>0.65557648104589672</v>
+        <f>G15/$G$12</f>
+        <v>0.6555764810458966</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -3384,11 +3298,11 @@
       </c>
       <c r="G16" s="8">
         <f>F16*Parameters!$C$11</f>
-        <v>0.29277527828238509</v>
+        <v>0.2927752782823851</v>
       </c>
       <c r="H16" s="8">
-        <f t="shared" si="2"/>
-        <v>0.62000829376442235</v>
+        <f>G16/$G$12</f>
+        <v>0.5710905529246325</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3419,8 +3333,8 @@
         <v>0.23723847071681164</v>
       </c>
       <c r="H17" s="8">
-        <f t="shared" si="2"/>
-        <v>0.50239835927178755</v>
+        <f>G17/$G$12</f>
+        <v>0.4627598689735741</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3444,11 +3358,11 @@
       </c>
       <c r="F18" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C18*PI()/180)*Parameters!$C$9*(1+(D18-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>5.99366935149424E-2</v>
+        <v>0.06507067380080576</v>
       </c>
       <c r="G18" s="8">
         <f>F18*Parameters!$C$11</f>
-        <v>0.1198733870298848</v>
+        <v>0.13014134760161153</v>
       </c>
       <c r="H18" s="8">
         <f>G18/$G$18</f>
@@ -3476,15 +3390,15 @@
       </c>
       <c r="F19" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C19*PI()/180)*Parameters!$C$9*(1+(D19-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>4.5932240329980535E-2</v>
+        <v>0.045932240329980535</v>
       </c>
       <c r="G19" s="8">
         <f>F19*Parameters!$C$11</f>
-        <v>9.186448065996107E-2</v>
+        <v>0.09186448065996107</v>
       </c>
       <c r="H19" s="8">
         <f>G19/$G$18</f>
-        <v>0.76634591660498397</v>
+        <v>0.7058823529411764</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -3508,15 +3422,15 @@
       </c>
       <c r="F20" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C20*PI()/180)*Parameters!$C$9*(1+(D20-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>3.2526363663601468E-2</v>
+        <v>0.03531246513211375</v>
       </c>
       <c r="G20" s="8">
         <f>F20*Parameters!$C$11</f>
-        <v>6.5052727327202936E-2</v>
+        <v>0.0706249302642275</v>
       </c>
       <c r="H20" s="8">
         <f>G20/$G$18</f>
-        <v>0.54267864568626134</v>
+        <v>0.5426786456862612</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -3540,15 +3454,15 @@
       </c>
       <c r="F21" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C21*PI()/180)*Parameters!$C$9*(1+(D21-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>2.4926445975609713E-2</v>
+        <v>0.024926445975609706</v>
       </c>
       <c r="G21" s="8">
         <f>F21*Parameters!$C$11</f>
-        <v>4.9852891951219426E-2</v>
+        <v>0.04985289195121941</v>
       </c>
       <c r="H21" s="8">
         <f>G21/$G$18</f>
-        <v>0.41587956415038935</v>
+        <v>0.3830672793079491</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -3572,11 +3486,11 @@
       </c>
       <c r="F22" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C22*PI()/180)*Parameters!$C$9*(1+(D22-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.16847212730962527</v>
+        <v>0.16847212730962524</v>
       </c>
       <c r="G22" s="8">
         <f>F22*Parameters!$C$11</f>
-        <v>0.33694425461925054</v>
+        <v>0.3369442546192505</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="2"/>
@@ -3593,7 +3507,7 @@
       </c>
       <c r="D23" s="9">
         <f>Parameters!H9</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3601,11 +3515,11 @@
       </c>
       <c r="F23" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C23*PI()/180)*Parameters!$C$9*(1+(D23-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.32500000000000001</v>
+        <v>0.20189</v>
       </c>
       <c r="G23" s="8">
         <f>F23*Parameters!$C$11</f>
-        <v>0.65</v>
+        <v>0.40378</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="2"/>

--- a/docs/diff_map.xlsx
+++ b/docs/diff_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_CBDF0786BF6CB24ED1E02AD36B93F9C32ED2E28A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B0D1AB-86EF-4D69-8F78-5A59BE54AB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graph" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
   <si>
     <t>Astral · Differential map</t>
   </si>
@@ -82,9 +82,6 @@
     <t>系数</t>
   </si>
   <si>
-    <t>基准 / 原 Q6</t>
-  </si>
-  <si>
     <t>每单位 n 修正</t>
   </si>
   <si>
@@ -133,24 +130,15 @@
     <t>角度以度输入，公式内部换算为弧度；n 是单侧数量，4+4 对应 n = 4，不是 8。</t>
   </si>
   <si>
-    <t>模型等效百分比 = c × 换算倍数；默认 35°、8+8 得到 c = 0.325，对应 65%。</t>
-  </si>
-  <si>
     <t>图表相对值 = 当前组合等效百分比 / 指定参考组合等效百分比；100% 不代表完全锁止。</t>
   </si>
   <si>
-    <t>前轴收油可用 72° / 80°，但 60° 前驱动 ramp 当前固定配 80°；后轴收油为 80°。</t>
-  </si>
-  <si>
     <t>本表计算斜面与摩擦面数量对应的模型系数，不包含 preload，也不是实测锁止扭矩曲线。</t>
   </si>
   <si>
     <t>来源：Astral_differential_F.jbeam、Astral_differential_R.jbeam；Excel 修改不会自动写回车辆。</t>
   </si>
   <si>
-    <t>原 Coast 区 72°、80° 的 4+4 / 6+6 标签均已纠正；所有图表结果改为公式引用。</t>
-  </si>
-  <si>
     <t>Astral · Differential samples</t>
   </si>
   <si>
@@ -173,6 +161,21 @@
   </si>
   <si>
     <t>Reference Q6</t>
+  </si>
+  <si>
+    <t>相对值以各图注明的参考组合为 100%；完整系数与模型等效百分比见 Samples。</t>
+  </si>
+  <si>
+    <t>锚点 / 原 Q6</t>
+  </si>
+  <si>
+    <t>模型等效百分比 = c × 换算倍数；35°、8+8 的 c = 0.37，对应 74%。</t>
+  </si>
+  <si>
+    <t>前轴收油可用 72° / 80°，但 65° 前驱动 ramp 当前固定配 80°；后轴收油为 80°。</t>
+  </si>
+  <si>
+    <t>FF = 1 + (n − 8) × 0.114；0.114 是 5/44 保留三位小数，8+8 锚点不变。</t>
   </si>
 </sst>
 </file>
@@ -325,13 +328,13 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -402,22 +405,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>46° / 6+6</c:v>
+                  <c:v>45° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>50° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46° / 4+4</c:v>
+                  <c:v>45° / 4+4</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>50° / 4+4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60° / 6+6</c:v>
+                  <c:v>62° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>60° / 4+4</c:v>
+                  <c:v>62° / 4+4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -432,19 +435,19 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8689131043745597</c:v>
+                  <c:v>0.8390996311772799</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7058823529411764</c:v>
+                  <c:v>0.7046632124352333</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6133504266173363</c:v>
+                  <c:v>0.5912826416586014</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.597863705421003</c:v>
+                  <c:v>0.5317094316614788</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.422021439120708</c:v>
+                  <c:v>0.37467607619668974</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -522,6 +525,7 @@
         <c:axId val="48672768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -648,7 +652,7 @@
                   <c:v>38° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44° / 6+6</c:v>
+                  <c:v>45° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>38° / 4+4</c:v>
@@ -657,7 +661,7 @@
                   <c:v>50° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44° / 4+4</c:v>
+                  <c:v>45° / 4+4</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>50° / 4+4</c:v>
@@ -675,19 +679,19 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8090449499765627</c:v>
+                  <c:v>0.7812856265067175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7058823529411765</c:v>
+                  <c:v>0.7046632124352333</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6555764810458966</c:v>
+                  <c:v>0.6555764810458967</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5710905529246325</c:v>
+                  <c:v>0.5505432394036974</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4627598689735741</c:v>
+                  <c:v>0.46196062913078734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -765,6 +769,7 @@
         <c:axId val="48672768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -888,16 +893,16 @@
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>72° / 6+6</c:v>
+                  <c:v>70° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>72° / 4+4</c:v>
+                  <c:v>70° / 4+4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>80° / 6+6</c:v>
+                  <c:v>85° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80° / 4+4</c:v>
+                  <c:v>85° / 4+4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -912,13 +917,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7058823529411764</c:v>
+                  <c:v>0.7046632124352332</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5426786456862612</c:v>
+                  <c:v>0.24037312749573927</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3830672793079491</c:v>
+                  <c:v>0.1693821002042515</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -996,6 +1001,7 @@
         <c:axId val="48672768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1436,10 +1442,8 @@
     </row>
     <row r="4" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>相对值以各图注明的参考组合为 100%；完整系数与模型等效百分比见 Samples。</t>
-        </is>
+      <c r="B4" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -1456,7 +1460,7 @@
       <c r="A5" s="2"/>
       <c r="B5" s="13" t="str">
         <f>"Front power："&amp;Samples!E6&amp;" = 100%"</f>
-        <v>Front power：46° / 6+6 = 100%</v>
+        <v>Front power：45° / 6+6 = 100%</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -1910,7 +1914,7 @@
       <c r="A37" s="2"/>
       <c r="B37" s="13" t="str">
         <f>"Coast："&amp;Samples!E18&amp;" = 100%"</f>
-        <v>Coast：72° / 6+6 = 100%</v>
+        <v>Coast：70° / 6+6 = 100%</v>
       </c>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -2269,17 +2273,17 @@
     </row>
     <row r="6" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -2317,7 +2321,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -2343,22 +2347,20 @@
         <v>13</v>
       </c>
       <c r="C9" s="5">
-        <v>0.20189</v>
+        <v>0.37</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>锚点 / 原 Q6</t>
-        </is>
+      <c r="F9" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G9" s="4">
         <v>35</v>
       </c>
       <c r="H9" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -2368,10 +2370,10 @@
     <row r="10" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5">
-        <v>0.20833333333333334</v>
+        <v>0.114</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -2388,13 +2390,13 @@
     <row r="11" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="4">
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -2435,17 +2437,17 @@
     </row>
     <row r="14" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2454,7 +2456,7 @@
     <row r="15" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>8</v>
@@ -2476,10 +2478,10 @@
     <row r="16" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="4">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -2499,7 +2501,7 @@
     <row r="17" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="4">
         <v>50</v>
@@ -2522,10 +2524,10 @@
     <row r="18" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="4">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -2540,7 +2542,7 @@
     <row r="19" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="4">
         <v>38</v>
@@ -2548,7 +2550,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
@@ -2560,15 +2562,15 @@
     <row r="20" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
@@ -2580,7 +2582,7 @@
     <row r="21" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4">
         <v>50</v>
@@ -2588,7 +2590,7 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
@@ -2600,15 +2602,15 @@
     <row r="22" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -2620,10 +2622,10 @@
     <row r="23" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -2651,122 +2653,122 @@
     </row>
     <row r="25" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
-      <c r="B25" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
+      <c r="B25" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
-      <c r="B26" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
+      <c r="B26" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
-      <c r="B27" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
+      <c r="B27" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>模型等效百分比 = c × 换算倍数；35°、4+4 的 c = 0.20189，对应 40.378%。</t>
-        </is>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
+      <c r="B28" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
-      <c r="B29" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
+      <c r="B29" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
-      <c r="B30" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>前轴收油可用 70° / 85°，但 62° 前驱动 ramp 当前固定配 85°；后轴收油为 85°。</t>
+        </is>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="B31" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
+      <c r="B31" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -2781,10 +2783,8 @@
     </row>
     <row r="33" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>FF 折中标定：保留 4+4；每侧增加一面，锚点系数增加 5/24。</t>
-        </is>
+      <c r="B33" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
@@ -2827,6 +2827,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="F20:K20"/>
+    <mergeCell ref="F21:K21"/>
+    <mergeCell ref="F22:K22"/>
+    <mergeCell ref="B25:K25"/>
     <mergeCell ref="B31:K31"/>
     <mergeCell ref="B32:K32"/>
     <mergeCell ref="B33:K33"/>
@@ -2835,17 +2846,6 @@
     <mergeCell ref="B28:K28"/>
     <mergeCell ref="B29:K29"/>
     <mergeCell ref="B30:K30"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="F20:K20"/>
-    <mergeCell ref="F21:K21"/>
-    <mergeCell ref="F22:K22"/>
-    <mergeCell ref="B25:K25"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B14:D14"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="2">
@@ -2892,7 +2892,7 @@
     <row r="2" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -2906,7 +2906,7 @@
     <row r="3" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -2932,10 +2932,10 @@
     <row r="5" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>9</v>
@@ -2944,13 +2944,13 @@
         <v>7</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -2958,11 +2958,11 @@
     <row r="6" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="9">
         <f>Parameters!C16</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="9">
         <f>Parameters!G17</f>
@@ -2970,18 +2970,18 @@
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" ref="E6:E23" si="0">C6&amp;"° / "&amp;D6&amp;"+"&amp;D6</f>
-        <v>46° / 6+6</v>
+        <v>45° / 6+6</v>
       </c>
       <c r="F6" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C6*PI()/180)*Parameters!$C$9*(1+(D6-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.19339553738080512</v>
+        <v>0.2000072812142215</v>
       </c>
       <c r="G6" s="8">
         <f>F6*Parameters!$C$11</f>
-        <v>0.38679107476161023</v>
+        <v>0.400014562428443</v>
       </c>
       <c r="H6" s="8">
-        <f>G6/$G$6</f>
+        <f t="shared" ref="H6:H11" si="1">G6/$G$6</f>
         <v>1</v>
       </c>
       <c r="I6" s="2"/>
@@ -2990,7 +2990,7 @@
     <row r="7" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="9">
         <f>Parameters!C17</f>
@@ -3006,15 +3006,15 @@
       </c>
       <c r="F7" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C7*PI()/180)*Parameters!$C$9*(1+(D7-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.16804391675774158</v>
+        <v>0.16782603589962378</v>
       </c>
       <c r="G7" s="8">
         <f>F7*Parameters!$C$11</f>
-        <v>0.33608783351548316</v>
+        <v>0.33565207179924755</v>
       </c>
       <c r="H7" s="8">
-        <f>G7/$G$6</f>
-        <v>0.8689131043745597</v>
+        <f t="shared" si="1"/>
+        <v>0.8390996311772799</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -3022,11 +3022,11 @@
     <row r="8" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="9">
         <f>Parameters!C16</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="9">
         <f>Parameters!G16</f>
@@ -3034,19 +3034,19 @@
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>46° / 4+4</v>
+        <v>45° / 4+4</v>
       </c>
       <c r="F8" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C8*PI()/180)*Parameters!$C$9*(1+(D8-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.13651449697468596</v>
+        <v>0.14093777329085042</v>
       </c>
       <c r="G8" s="8">
         <f>F8*Parameters!$C$11</f>
-        <v>0.2730289939493719</v>
+        <v>0.28187554658170083</v>
       </c>
       <c r="H8" s="8">
-        <f>G8/$G$6</f>
-        <v>0.7058823529411764</v>
+        <f t="shared" si="1"/>
+        <v>0.7046632124352333</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -3054,7 +3054,7 @@
     <row r="9" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="9">
         <f>Parameters!C17</f>
@@ -3070,15 +3070,15 @@
       </c>
       <c r="F9" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C9*PI()/180)*Parameters!$C$9*(1+(D9-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.11861923535840582</v>
+        <v>0.11826083358729966</v>
       </c>
       <c r="G9" s="8">
         <f>F9*Parameters!$C$11</f>
-        <v>0.23723847071681164</v>
+        <v>0.23652166717459933</v>
       </c>
       <c r="H9" s="8">
-        <f>G9/$G$6</f>
-        <v>0.6133504266173363</v>
+        <f t="shared" si="1"/>
+        <v>0.5912826416586014</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -3086,11 +3086,11 @@
     <row r="10" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="9">
         <f>Parameters!C18</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D10" s="9">
         <f>Parameters!G17</f>
@@ -3098,19 +3098,19 @@
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>60° / 6+6</v>
+        <v>62° / 6+6</v>
       </c>
       <c r="F10" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C10*PI()/180)*Parameters!$C$9*(1+(D10-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.11562417259037425</v>
+        <v>0.10634575782257129</v>
       </c>
       <c r="G10" s="8">
         <f>F10*Parameters!$C$11</f>
-        <v>0.2312483451807485</v>
+        <v>0.21269151564514258</v>
       </c>
       <c r="H10" s="8">
-        <f>G10/$G$6</f>
-        <v>0.597863705421003</v>
+        <f t="shared" si="1"/>
+        <v>0.5317094316614788</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -3118,11 +3118,11 @@
     <row r="11" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="9">
         <f>Parameters!C18</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D11" s="9">
         <f>Parameters!G16</f>
@@ -3130,19 +3130,19 @@
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>60° / 4+4</v>
+        <v>62° / 4+4</v>
       </c>
       <c r="F11" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C11*PI()/180)*Parameters!$C$9*(1+(D11-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.08161706300497006</v>
+        <v>0.07493794333611241</v>
       </c>
       <c r="G11" s="8">
         <f>F11*Parameters!$C$11</f>
-        <v>0.1632341260099401</v>
+        <v>0.14987588667222482</v>
       </c>
       <c r="H11" s="8">
-        <f>G11/$G$6</f>
-        <v>0.422021439120708</v>
+        <f t="shared" si="1"/>
+        <v>0.37467607619668974</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -3150,7 +3150,7 @@
     <row r="12" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="9">
         <f>Parameters!C19</f>
@@ -3166,14 +3166,14 @@
       </c>
       <c r="F12" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C12*PI()/180)*Parameters!$C$9*(1+(D12-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.25632999599016565</v>
+        <v>0.25599764596783076</v>
       </c>
       <c r="G12" s="8">
         <f>F12*Parameters!$C$11</f>
-        <v>0.5126599919803313</v>
+        <v>0.5119952919356615</v>
       </c>
       <c r="H12" s="8">
-        <f>G12/$G$12</f>
+        <f t="shared" ref="H12:H17" si="2">G12/$G$12</f>
         <v>1</v>
       </c>
       <c r="I12" s="2"/>
@@ -3182,11 +3182,11 @@
     <row r="13" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="9">
         <f>Parameters!C20</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="9">
         <f>Parameters!G17</f>
@@ -3194,19 +3194,19 @@
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>44° / 6+6</v>
+        <v>45° / 6+6</v>
       </c>
       <c r="F13" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C13*PI()/180)*Parameters!$C$9*(1+(D13-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.2073824887833561</v>
+        <v>0.2000072812142215</v>
       </c>
       <c r="G13" s="8">
         <f>F13*Parameters!$C$11</f>
-        <v>0.4147649775667122</v>
+        <v>0.400014562428443</v>
       </c>
       <c r="H13" s="8">
-        <f>G13/$G$12</f>
-        <v>0.8090449499765627</v>
+        <f t="shared" si="2"/>
+        <v>0.7812856265067175</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -3214,7 +3214,7 @@
     <row r="14" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="9">
         <f>Parameters!C19</f>
@@ -3230,15 +3230,15 @@
       </c>
       <c r="F14" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C14*PI()/180)*Parameters!$C$9*(1+(D14-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.18093882069894046</v>
+        <v>0.18039212358354917</v>
       </c>
       <c r="G14" s="8">
         <f>F14*Parameters!$C$11</f>
-        <v>0.3618776413978809</v>
+        <v>0.36078424716709834</v>
       </c>
       <c r="H14" s="8">
-        <f>G14/$G$12</f>
-        <v>0.7058823529411765</v>
+        <f t="shared" si="2"/>
+        <v>0.7046632124352333</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -3246,7 +3246,7 @@
     <row r="15" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="9">
         <f>Parameters!C21</f>
@@ -3262,15 +3262,15 @@
       </c>
       <c r="F15" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C15*PI()/180)*Parameters!$C$9*(1+(D15-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.16804391675774158</v>
+        <v>0.16782603589962378</v>
       </c>
       <c r="G15" s="8">
         <f>F15*Parameters!$C$11</f>
-        <v>0.33608783351548316</v>
+        <v>0.33565207179924755</v>
       </c>
       <c r="H15" s="8">
-        <f>G15/$G$12</f>
-        <v>0.6555764810458966</v>
+        <f t="shared" si="2"/>
+        <v>0.6555764810458967</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -3278,11 +3278,11 @@
     <row r="16" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="9">
         <f>Parameters!C20</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="9">
         <f>Parameters!G16</f>
@@ -3290,19 +3290,19 @@
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>44° / 4+4</v>
+        <v>45° / 4+4</v>
       </c>
       <c r="F16" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C16*PI()/180)*Parameters!$C$9*(1+(D16-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.14638763914119254</v>
+        <v>0.14093777329085042</v>
       </c>
       <c r="G16" s="8">
         <f>F16*Parameters!$C$11</f>
-        <v>0.2927752782823851</v>
+        <v>0.28187554658170083</v>
       </c>
       <c r="H16" s="8">
-        <f>G16/$G$12</f>
-        <v>0.5710905529246325</v>
+        <f t="shared" si="2"/>
+        <v>0.5505432394036974</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3310,7 +3310,7 @@
     <row r="17" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="9">
         <f>Parameters!C21</f>
@@ -3326,15 +3326,15 @@
       </c>
       <c r="F17" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C17*PI()/180)*Parameters!$C$9*(1+(D17-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.11861923535840582</v>
+        <v>0.11826083358729966</v>
       </c>
       <c r="G17" s="8">
         <f>F17*Parameters!$C$11</f>
-        <v>0.23723847071681164</v>
+        <v>0.23652166717459933</v>
       </c>
       <c r="H17" s="8">
-        <f>G17/$G$12</f>
-        <v>0.4627598689735741</v>
+        <f t="shared" si="2"/>
+        <v>0.46196062913078734</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3342,11 +3342,11 @@
     <row r="18" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" s="9">
         <f>Parameters!C22</f>
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D18" s="9">
         <f>Parameters!G17</f>
@@ -3354,15 +3354,15 @@
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>72° / 6+6</v>
+        <v>70° / 6+6</v>
       </c>
       <c r="F18" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C18*PI()/180)*Parameters!$C$9*(1+(D18-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.06507067380080576</v>
+        <v>0.07279669699848643</v>
       </c>
       <c r="G18" s="8">
         <f>F18*Parameters!$C$11</f>
-        <v>0.13014134760161153</v>
+        <v>0.14559339399697285</v>
       </c>
       <c r="H18" s="8">
         <f>G18/$G$18</f>
@@ -3374,11 +3374,11 @@
     <row r="19" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="9">
         <f>Parameters!C22</f>
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D19" s="9">
         <f>Parameters!G16</f>
@@ -3386,19 +3386,19 @@
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>72° / 4+4</v>
+        <v>70° / 4+4</v>
       </c>
       <c r="F19" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C19*PI()/180)*Parameters!$C$9*(1+(D19-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.045932240329980535</v>
+        <v>0.051297154361627746</v>
       </c>
       <c r="G19" s="8">
         <f>F19*Parameters!$C$11</f>
-        <v>0.09186448065996107</v>
+        <v>0.10259430872325549</v>
       </c>
       <c r="H19" s="8">
         <f>G19/$G$18</f>
-        <v>0.7058823529411764</v>
+        <v>0.7046632124352332</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -3406,11 +3406,11 @@
     <row r="20" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="9">
         <f>Parameters!C23</f>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D20" s="9">
         <f>Parameters!G17</f>
@@ -3418,19 +3418,19 @@
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>80° / 6+6</v>
+        <v>85° / 6+6</v>
       </c>
       <c r="F20" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C20*PI()/180)*Parameters!$C$9*(1+(D20-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.03531246513211375</v>
+        <v>0.01749836972888588</v>
       </c>
       <c r="G20" s="8">
         <f>F20*Parameters!$C$11</f>
-        <v>0.0706249302642275</v>
+        <v>0.03499673945777176</v>
       </c>
       <c r="H20" s="8">
         <f>G20/$G$18</f>
-        <v>0.5426786456862612</v>
+        <v>0.24037312749573927</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -3438,11 +3438,11 @@
     <row r="21" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="9">
         <f>Parameters!C23</f>
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D21" s="9">
         <f>Parameters!G16</f>
@@ -3450,19 +3450,19 @@
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>80° / 4+4</v>
+        <v>85° / 4+4</v>
       </c>
       <c r="F21" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C21*PI()/180)*Parameters!$C$9*(1+(D21-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.024926445975609706</v>
+        <v>0.012330457425536163</v>
       </c>
       <c r="G21" s="8">
         <f>F21*Parameters!$C$11</f>
-        <v>0.04985289195121941</v>
+        <v>0.024660914851072326</v>
       </c>
       <c r="H21" s="8">
         <f>G21/$G$18</f>
-        <v>0.3830672793079491</v>
+        <v>0.1693821002042515</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -3470,7 +3470,7 @@
     <row r="22" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C22" s="9">
         <f>Parameters!G8</f>
@@ -3486,11 +3486,11 @@
       </c>
       <c r="F22" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C22*PI()/180)*Parameters!$C$9*(1+(D22-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.16847212730962524</v>
+        <v>0.16796309765159925</v>
       </c>
       <c r="G22" s="8">
         <f>F22*Parameters!$C$11</f>
-        <v>0.3369442546192505</v>
+        <v>0.3359261953031985</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="2"/>
@@ -3499,7 +3499,7 @@
     <row r="23" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C23" s="9">
         <f>Parameters!G9</f>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="D23" s="9">
         <f>Parameters!H9</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3515,11 +3515,11 @@
       </c>
       <c r="F23" s="7">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C23*PI()/180)*Parameters!$C$9*(1+(D23-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.20189</v>
+        <v>0.37</v>
       </c>
       <c r="G23" s="8">
         <f>F23*Parameters!$C$11</f>
-        <v>0.40378</v>
+        <v>0.74</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="2"/>

--- a/docs/diff_map.xlsx
+++ b/docs/diff_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B0D1AB-86EF-4D69-8F78-5A59BE54AB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99765EDB-0641-4162-AA91-CF6C903CC1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graph" sheetId="1" r:id="rId1"/>
@@ -35,15 +35,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
-  <si>
-    <t>Astral · Differential map</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
   <si>
     <t>Astral · Differential parameters</t>
-  </si>
-  <si>
-    <t>黄色单元格可编辑；表格沿用当前 JBeam 的计算模型。</t>
   </si>
   <si>
     <t>模型基准</t>
@@ -106,43 +100,10 @@
     <t>Rear power</t>
   </si>
   <si>
-    <t>图表的 100% 参考组合</t>
-  </si>
-  <si>
-    <t>前驱动：第一组前 ramp + 第二组 n</t>
-  </si>
-  <si>
-    <t>后驱动：第一组后 ramp + 第二组 n</t>
-  </si>
-  <si>
     <t>Coast</t>
   </si>
   <si>
-    <t>收油：第一组 coast ramp + 第二组 n</t>
-  </si>
-  <si>
-    <t>计算与说明</t>
-  </si>
-  <si>
-    <t>游戏系数 c = tan(参考角度) / tan(ramp 角度) × 参考系数 × [1 + (n − 参考 n) × 修正系数]。</t>
-  </si>
-  <si>
-    <t>角度以度输入，公式内部换算为弧度；n 是单侧数量，4+4 对应 n = 4，不是 8。</t>
-  </si>
-  <si>
-    <t>图表相对值 = 当前组合等效百分比 / 指定参考组合等效百分比；100% 不代表完全锁止。</t>
-  </si>
-  <si>
-    <t>本表计算斜面与摩擦面数量对应的模型系数，不包含 preload，也不是实测锁止扭矩曲线。</t>
-  </si>
-  <si>
-    <t>来源：Astral_differential_F.jbeam、Astral_differential_R.jbeam；Excel 修改不会自动写回车辆。</t>
-  </si>
-  <si>
     <t>Astral · Differential samples</t>
-  </si>
-  <si>
-    <t>离散 ramp / 摩擦面组合计算。系数 c 直接对应游戏参数；等效百分比沿用原表 ×2 口径。</t>
   </si>
   <si>
     <t>Ramp (°)</t>
@@ -163,19 +124,11 @@
     <t>Reference Q6</t>
   </si>
   <si>
-    <t>相对值以各图注明的参考组合为 100%；完整系数与模型等效百分比见 Samples。</t>
-  </si>
-  <si>
     <t>锚点 / 原 Q6</t>
   </si>
   <si>
-    <t>模型等效百分比 = c × 换算倍数；35°、8+8 的 c = 0.37，对应 74%。</t>
-  </si>
-  <si>
-    <t>前轴收油可用 72° / 80°，但 65° 前驱动 ramp 当前固定配 80°；后轴收油为 80°。</t>
-  </si>
-  <si>
-    <t>FF = 1 + (n − 8) × 0.114；0.114 是 5/44 保留三位小数，8+8 锚点不变。</t>
+    <t>Astral · Differential map</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -186,7 +139,7 @@
     <numFmt numFmtId="176" formatCode="0.0000"/>
     <numFmt numFmtId="177" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,45 +149,21 @@
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF283C50"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF667B91"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF195DB1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF283C50"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF31475E"/>
-      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -242,8 +171,146 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667B91"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF195DB1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF283C50"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -257,7 +324,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -267,16 +359,254 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE9EEF3"/>
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31475E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="21">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDCE4EB"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -285,7 +615,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -295,46 +625,76 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="22" fillId="21" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="177" fontId="24" fillId="23" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="25" fillId="24" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -370,7 +730,7 @@
             <a:r>
               <a:rPr lang="en-US" sz="1125">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
               <a:t>Front power</a:t>
@@ -435,16 +795,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8390996311772799</c:v>
+                  <c:v>0.83909963117727993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7046632124352333</c:v>
+                  <c:v>0.70466321243523333</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5912826416586014</c:v>
+                  <c:v>0.59128264165860145</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5317094316614788</c:v>
+                  <c:v>0.53170943166147877</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.37467607619668974</c:v>
@@ -507,7 +867,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -565,7 +925,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -614,7 +974,7 @@
             <a:r>
               <a:rPr lang="en-US" sz="1125">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
               <a:t>Rear power</a:t>
@@ -679,16 +1039,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7812856265067175</c:v>
+                  <c:v>0.78128562650671751</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7046632124352333</c:v>
+                  <c:v>0.70466321243523333</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6555764810458967</c:v>
+                  <c:v>0.65557648104589672</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5505432394036974</c:v>
+                  <c:v>0.55054323940369743</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.46196062913078734</c:v>
@@ -751,7 +1111,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -809,7 +1169,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -858,7 +1218,7 @@
             <a:r>
               <a:rPr lang="en-US" sz="1125">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
               <a:t>Coast</a:t>
@@ -917,13 +1277,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7046632124352332</c:v>
+                  <c:v>0.70466321243523322</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.24037312749573927</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1693821002042515</c:v>
+                  <c:v>0.16938210020425151</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -983,7 +1343,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -1041,7 +1401,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
+                <a:ea typeface="微软雅黑"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -1396,7 +1756,7 @@
     <col min="17" max="17" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1410,20 +1770,20 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
+      <c r="B2" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
@@ -1442,35 +1802,23 @@
     </row>
     <row r="4" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="13" t="str">
+      <c r="B5" s="25" t="str">
         <f>"Front power："&amp;Samples!E6&amp;" = 100%"</f>
         <v>Front power：45° / 6+6 = 100%</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
       <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
@@ -1683,21 +2031,21 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
-      <c r="B21" s="13" t="str">
+      <c r="B21" s="25" t="str">
         <f>"Rear power："&amp;Samples!E12&amp;" = 100%"</f>
         <v>Rear power：38° / 6+6 = 100%</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
@@ -1910,21 +2258,21 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
-      <c r="B37" s="13" t="str">
+      <c r="B37" s="25" t="str">
         <f>"Coast："&amp;Samples!E18&amp;" = 100%"</f>
         <v>Coast：70° / 6+6 = 100%</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
       <c r="L37" s="2"/>
     </row>
     <row r="38" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
@@ -2166,14 +2514,13 @@
       <c r="L54" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B4:K4"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="B21:K21"/>
     <mergeCell ref="B37:K37"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2197,7 +2544,7 @@
     <col min="9" max="12" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2211,20 +2558,20 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
+      <c r="B2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
@@ -2243,18 +2590,6 @@
     </row>
     <row r="4" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
@@ -2271,69 +2606,69 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
+      <c r="F6" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5">
+        <v>35</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>40</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <v>4</v>
       </c>
       <c r="I8" s="2"/>
@@ -2341,25 +2676,25 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="10">
         <v>0.37</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="F9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="5">
         <v>35</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <v>8</v>
       </c>
       <c r="I9" s="2"/>
@@ -2367,16 +2702,16 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="10">
         <v>0.114</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>14</v>
+      <c r="D10" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -2387,16 +2722,16 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5">
         <v>2</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -2435,19 +2770,19 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
+      <c r="B14" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="F14" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2455,19 +2790,19 @@
     </row>
     <row r="15" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="6"/>
+      <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -2475,21 +2810,21 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="B16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="5">
         <v>45</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2" t="str">
+      <c r="F16" s="11" t="str">
         <f>G16&amp;"+"&amp;G16</f>
         <v>4+4</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="5">
         <v>4</v>
       </c>
       <c r="H16" s="2"/>
@@ -2498,21 +2833,21 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="5">
         <v>50</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2" t="str">
+      <c r="F17" s="12" t="str">
         <f>G17&amp;"+"&amp;G17</f>
         <v>6+6</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="5">
         <v>6</v>
       </c>
       <c r="H17" s="2"/>
@@ -2521,12 +2856,12 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="B18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="5">
         <v>62</v>
       </c>
       <c r="D18" s="2"/>
@@ -2539,92 +2874,60 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="B19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="5">
         <v>38</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="B20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="5">
         <v>45</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="4">
+      <c r="B21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="5">
         <v>50</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="4">
+      <c r="B22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="5">
         <v>70</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="4">
+      <c r="B23" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="5">
         <v>85</v>
       </c>
       <c r="D23" s="2"/>
@@ -2651,150 +2954,40 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
-      <c r="B25" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
-      <c r="B26" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
-      <c r="B27" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
-      <c r="B28" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
-      <c r="B29" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>前轴收油可用 70° / 85°，但 62° 前驱动 ramp 当前固定配 85°；后轴收油为 85°。</t>
-        </is>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="B31" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
-      <c r="B32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
-      <c r="B33" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
@@ -2826,28 +3019,14 @@
       <c r="L35" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="5">
     <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B4:K4"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="F20:K20"/>
-    <mergeCell ref="F21:K21"/>
-    <mergeCell ref="F22:K22"/>
-    <mergeCell ref="B25:K25"/>
-    <mergeCell ref="B31:K31"/>
-    <mergeCell ref="B32:K32"/>
-    <mergeCell ref="B33:K33"/>
-    <mergeCell ref="B26:K26"/>
-    <mergeCell ref="B27:K27"/>
-    <mergeCell ref="B28:K28"/>
-    <mergeCell ref="B29:K29"/>
-    <mergeCell ref="B30:K30"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="decimal" sqref="C7 G8:G9 C16:C23" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>1</formula1>
@@ -2877,7 +3056,7 @@
     <col min="9" max="10" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2889,32 +3068,22 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
+      <c r="B2" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
@@ -2929,599 +3098,599 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="B5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>39</v>
+      <c r="E5" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="9">
+      <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="15">
         <f>Parameters!C16</f>
         <v>45</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="15">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
-      <c r="E6" s="2" t="str">
+      <c r="E6" s="11" t="str">
         <f t="shared" ref="E6:E23" si="0">C6&amp;"° / "&amp;D6&amp;"+"&amp;D6</f>
         <v>45° / 6+6</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="16">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C6*PI()/180)*Parameters!$C$9*(1+(D6-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.2000072812142215</v>
-      </c>
-      <c r="G6" s="8">
+        <v>0.20000728121422151</v>
+      </c>
+      <c r="G6" s="17">
         <f>F6*Parameters!$C$11</f>
-        <v>0.400014562428443</v>
-      </c>
-      <c r="H6" s="8">
+        <v>0.40001456242844302</v>
+      </c>
+      <c r="H6" s="17">
         <f t="shared" ref="H6:H11" si="1">G6/$G$6</f>
         <v>1</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="B7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="18">
         <f>Parameters!C17</f>
         <v>50</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="18">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
-      <c r="E7" s="2" t="str">
+      <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>50° / 6+6</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="19">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C7*PI()/180)*Parameters!$C$9*(1+(D7-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.16782603589962378</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="20">
         <f>F7*Parameters!$C$11</f>
         <v>0.33565207179924755</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="20">
         <f t="shared" si="1"/>
-        <v>0.8390996311772799</v>
+        <v>0.83909963117727993</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="9">
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="15">
         <f>Parameters!C16</f>
         <v>45</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="15">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
-      <c r="E8" s="2" t="str">
+      <c r="E8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>45° / 4+4</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="16">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C8*PI()/180)*Parameters!$C$9*(1+(D8-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.14093777329085042</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="17">
         <f>F8*Parameters!$C$11</f>
         <v>0.28187554658170083</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="17">
         <f t="shared" si="1"/>
-        <v>0.7046632124352333</v>
+        <v>0.70466321243523333</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="9">
+      <c r="B9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="18">
         <f>Parameters!C17</f>
         <v>50</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="18">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
-      <c r="E9" s="2" t="str">
+      <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>50° / 4+4</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="19">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C9*PI()/180)*Parameters!$C$9*(1+(D9-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.11826083358729966</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="20">
         <f>F9*Parameters!$C$11</f>
         <v>0.23652166717459933</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="20">
         <f t="shared" si="1"/>
-        <v>0.5912826416586014</v>
+        <v>0.59128264165860145</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="9">
+      <c r="B10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="15">
         <f>Parameters!C18</f>
         <v>62</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="15">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
-      <c r="E10" s="2" t="str">
+      <c r="E10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>62° / 6+6</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="16">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C10*PI()/180)*Parameters!$C$9*(1+(D10-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.10634575782257129</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="17">
         <f>F10*Parameters!$C$11</f>
         <v>0.21269151564514258</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>0.5317094316614788</v>
+        <v>0.53170943166147877</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="9">
+      <c r="B11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="18">
         <f>Parameters!C18</f>
         <v>62</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="18">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
-      <c r="E11" s="2" t="str">
+      <c r="E11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>62° / 4+4</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="19">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C11*PI()/180)*Parameters!$C$9*(1+(D11-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.07493794333611241</v>
-      </c>
-      <c r="G11" s="8">
+        <v>7.4937943336112409E-2</v>
+      </c>
+      <c r="G11" s="20">
         <f>F11*Parameters!$C$11</f>
         <v>0.14987588667222482</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="20">
         <f t="shared" si="1"/>
         <v>0.37467607619668974</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="9">
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="15">
         <f>Parameters!C19</f>
         <v>38</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="15">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
-      <c r="E12" s="2" t="str">
+      <c r="E12" s="11" t="str">
         <f t="shared" si="0"/>
         <v>38° / 6+6</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="16">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C12*PI()/180)*Parameters!$C$9*(1+(D12-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.25599764596783076</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="17">
         <f>F12*Parameters!$C$11</f>
-        <v>0.5119952919356615</v>
-      </c>
-      <c r="H12" s="8">
+        <v>0.51199529193566151</v>
+      </c>
+      <c r="H12" s="17">
         <f t="shared" ref="H12:H17" si="2">G12/$G$12</f>
         <v>1</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="9">
+      <c r="B13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="18">
         <f>Parameters!C20</f>
         <v>45</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="18">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
-      <c r="E13" s="2" t="str">
+      <c r="E13" s="12" t="str">
         <f t="shared" si="0"/>
         <v>45° / 6+6</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="19">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C13*PI()/180)*Parameters!$C$9*(1+(D13-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.2000072812142215</v>
-      </c>
-      <c r="G13" s="8">
+        <v>0.20000728121422151</v>
+      </c>
+      <c r="G13" s="20">
         <f>F13*Parameters!$C$11</f>
-        <v>0.400014562428443</v>
-      </c>
-      <c r="H13" s="8">
+        <v>0.40001456242844302</v>
+      </c>
+      <c r="H13" s="20">
         <f t="shared" si="2"/>
-        <v>0.7812856265067175</v>
+        <v>0.78128562650671751</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="9">
+      <c r="B14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="15">
         <f>Parameters!C19</f>
         <v>38</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="15">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
-      <c r="E14" s="2" t="str">
+      <c r="E14" s="11" t="str">
         <f t="shared" si="0"/>
         <v>38° / 4+4</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="16">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C14*PI()/180)*Parameters!$C$9*(1+(D14-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.18039212358354917</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="17">
         <f>F14*Parameters!$C$11</f>
         <v>0.36078424716709834</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="17">
         <f t="shared" si="2"/>
-        <v>0.7046632124352333</v>
+        <v>0.70466321243523333</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="9">
+      <c r="B15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="18">
         <f>Parameters!C21</f>
         <v>50</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="18">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
-      <c r="E15" s="2" t="str">
+      <c r="E15" s="12" t="str">
         <f t="shared" si="0"/>
         <v>50° / 6+6</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="19">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C15*PI()/180)*Parameters!$C$9*(1+(D15-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.16782603589962378</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="20">
         <f>F15*Parameters!$C$11</f>
         <v>0.33565207179924755</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="20">
         <f t="shared" si="2"/>
-        <v>0.6555764810458967</v>
+        <v>0.65557648104589672</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="9">
+      <c r="B16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="15">
         <f>Parameters!C20</f>
         <v>45</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="15">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
-      <c r="E16" s="2" t="str">
+      <c r="E16" s="11" t="str">
         <f t="shared" si="0"/>
         <v>45° / 4+4</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="16">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C16*PI()/180)*Parameters!$C$9*(1+(D16-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.14093777329085042</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="17">
         <f>F16*Parameters!$C$11</f>
         <v>0.28187554658170083</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="17">
         <f t="shared" si="2"/>
-        <v>0.5505432394036974</v>
+        <v>0.55054323940369743</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="9">
+      <c r="B17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="18">
         <f>Parameters!C21</f>
         <v>50</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="18">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
-      <c r="E17" s="2" t="str">
+      <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
         <v>50° / 4+4</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="19">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C17*PI()/180)*Parameters!$C$9*(1+(D17-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.11826083358729966</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="20">
         <f>F17*Parameters!$C$11</f>
         <v>0.23652166717459933</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="20">
         <f t="shared" si="2"/>
         <v>0.46196062913078734</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="9">
+      <c r="B18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="15">
         <f>Parameters!C22</f>
         <v>70</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="15">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
-      <c r="E18" s="2" t="str">
+      <c r="E18" s="11" t="str">
         <f t="shared" si="0"/>
         <v>70° / 6+6</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="16">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C18*PI()/180)*Parameters!$C$9*(1+(D18-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.07279669699848643</v>
-      </c>
-      <c r="G18" s="8">
+        <v>7.2796696998486426E-2</v>
+      </c>
+      <c r="G18" s="17">
         <f>F18*Parameters!$C$11</f>
         <v>0.14559339399697285</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="17">
         <f>G18/$G$18</f>
         <v>1</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="9">
+      <c r="B19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="18">
         <f>Parameters!C22</f>
         <v>70</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="18">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
-      <c r="E19" s="2" t="str">
+      <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
         <v>70° / 4+4</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="19">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C19*PI()/180)*Parameters!$C$9*(1+(D19-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.051297154361627746</v>
-      </c>
-      <c r="G19" s="8">
+        <v>5.1297154361627746E-2</v>
+      </c>
+      <c r="G19" s="20">
         <f>F19*Parameters!$C$11</f>
         <v>0.10259430872325549</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="20">
         <f>G19/$G$18</f>
-        <v>0.7046632124352332</v>
+        <v>0.70466321243523322</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="9">
+      <c r="B20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="15">
         <f>Parameters!C23</f>
         <v>85</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="15">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
-      <c r="E20" s="2" t="str">
+      <c r="E20" s="11" t="str">
         <f t="shared" si="0"/>
         <v>85° / 6+6</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="16">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C20*PI()/180)*Parameters!$C$9*(1+(D20-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.01749836972888588</v>
-      </c>
-      <c r="G20" s="8">
+        <v>1.7498369728885878E-2</v>
+      </c>
+      <c r="G20" s="17">
         <f>F20*Parameters!$C$11</f>
-        <v>0.03499673945777176</v>
-      </c>
-      <c r="H20" s="8">
+        <v>3.4996739457771757E-2</v>
+      </c>
+      <c r="H20" s="17">
         <f>G20/$G$18</f>
         <v>0.24037312749573927</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="B21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="18">
         <f>Parameters!C23</f>
         <v>85</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="18">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
-      <c r="E21" s="2" t="str">
+      <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
         <v>85° / 4+4</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="19">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C21*PI()/180)*Parameters!$C$9*(1+(D21-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.012330457425536163</v>
-      </c>
-      <c r="G21" s="8">
+        <v>1.2330457425536163E-2</v>
+      </c>
+      <c r="G21" s="20">
         <f>F21*Parameters!$C$11</f>
-        <v>0.024660914851072326</v>
-      </c>
-      <c r="H21" s="8">
+        <v>2.4660914851072326E-2</v>
+      </c>
+      <c r="H21" s="20">
         <f>G21/$G$18</f>
-        <v>0.1693821002042515</v>
+        <v>0.16938210020425151</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="9">
+      <c r="B22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="15">
         <f>Parameters!G8</f>
         <v>40</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="15">
         <f>Parameters!H8</f>
         <v>4</v>
       </c>
-      <c r="E22" s="2" t="str">
+      <c r="E22" s="11" t="str">
         <f t="shared" si="0"/>
         <v>40° / 4+4</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="16">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C22*PI()/180)*Parameters!$C$9*(1+(D22-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.16796309765159925</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="17">
         <f>F22*Parameters!$C$11</f>
         <v>0.3359261953031985</v>
       </c>
-      <c r="H22" s="8"/>
+      <c r="H22" s="17"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="9">
+      <c r="B23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="18">
         <f>Parameters!G9</f>
         <v>35</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="18">
         <f>Parameters!H9</f>
         <v>8</v>
       </c>
-      <c r="E23" s="2" t="str">
+      <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
         <v>35° / 8+8</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="19">
         <f>TAN(Parameters!$C$7*PI()/180)/TAN(C23*PI()/180)*Parameters!$C$9*(1+(D23-Parameters!$C$8)*Parameters!$C$10)</f>
         <v>0.37</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="20">
         <f>F23*Parameters!$C$11</f>
         <v>0.74</v>
       </c>
-      <c r="H23" s="8"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
@@ -3562,11 +3731,10 @@
       <c r="J26" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/diff_map.xlsx
+++ b/docs/diff_map.xlsx
@@ -615,7 +615,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -697,6 +697,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -765,13 +768,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>45° / 6+6</c:v>
+                  <c:v>46° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>50° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45° / 4+4</c:v>
+                  <c:v>46° / 4+4</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>50° / 4+4</c:v>
@@ -795,19 +798,19 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.83909963117727993</c:v>
+                  <c:v>0.8646842979195788</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.70466321243523333</c:v>
+                  <c:v>0.6666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.59128264165860145</c:v>
+                  <c:v>0.5764561986130526</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.53170943166147877</c:v>
+                  <c:v>0.5241827435579796</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37467607619668974</c:v>
+                  <c:v>0.34945516237198637</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1009,22 +1012,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>38° / 6+6</c:v>
+                  <c:v>40° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45° / 6+6</c:v>
+                  <c:v>46° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38° / 4+4</c:v>
+                  <c:v>40° / 4+4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>50° / 6+6</c:v>
+                  <c:v>54° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45° / 4+4</c:v>
+                  <c:v>46° / 4+4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50° / 4+4</c:v>
+                  <c:v>54° / 4+4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1039,19 +1042,19 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.78128562650671751</c:v>
+                  <c:v>0.8097840331950072</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.70466321243523333</c:v>
+                  <c:v>0.6666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.65557648104589672</c:v>
+                  <c:v>0.6008606190275605</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.55054323940369743</c:v>
+                  <c:v>0.5398560221300048</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.46196062913078734</c:v>
+                  <c:v>0.4005737460183737</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1259,10 +1262,10 @@
                   <c:v>70° / 4+4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>85° / 6+6</c:v>
+                  <c:v>80° / 6+6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>85° / 4+4</c:v>
+                  <c:v>80° / 4+4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1277,13 +1280,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.70466321243523322</c:v>
+                  <c:v>0.6666666666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.24037312749573927</c:v>
+                  <c:v>0.3265121373650463</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.16938210020425151</c:v>
+                  <c:v>0.21767475824336424</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1808,7 +1811,7 @@
       <c r="A5" s="2"/>
       <c r="B5" s="25" t="str">
         <f>"Front power："&amp;Samples!E6&amp;" = 100%"</f>
-        <v>Front power：45° / 6+6 = 100%</v>
+        <v>Front power：46° / 6+6 = 100%</v>
       </c>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
@@ -2035,7 +2038,7 @@
       <c r="A21" s="2"/>
       <c r="B21" s="25" t="str">
         <f>"Rear power："&amp;Samples!E12&amp;" = 100%"</f>
-        <v>Rear power：38° / 6+6 = 100%</v>
+        <v>Rear power：40° / 6+6 = 100%</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -2626,11 +2629,13 @@
     </row>
     <row r="7" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="4" t="s">
-        <v>3</v>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Ramp 角度补偿</t>
+        </is>
       </c>
       <c r="C7" s="5">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>4</v>
@@ -2662,8 +2667,10 @@
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="4" t="s">
-        <v>10</v>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>校核 1</t>
+        </is>
       </c>
       <c r="G8" s="5">
         <v>40</v>
@@ -2678,18 +2685,22 @@
     </row>
     <row r="9" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="4" t="s">
-        <v>11</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>基础游戏系数</t>
+        </is>
       </c>
       <c r="C9" s="10">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="8" t="s">
-        <v>29</v>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>校核 2</t>
+        </is>
       </c>
       <c r="G9" s="5">
         <v>35</v>
@@ -2704,15 +2715,9 @@
     </row>
     <row r="10" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="10">
-        <v>0.114</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -2816,7 +2821,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -2880,7 +2885,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -2892,7 +2897,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -2904,7 +2909,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="5">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -2928,7 +2933,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -3131,26 +3136,26 @@
       </c>
       <c r="C6" s="15">
         <f>Parameters!C16</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="15">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
       <c r="E6" s="11" t="str">
-        <f t="shared" ref="E6:E23" si="0">C6&amp;"° / "&amp;D6&amp;"+"&amp;D6</f>
-        <v>45° / 6+6</v>
+        <f>C6&amp;"° / "&amp;D6&amp;"+"&amp;D6</f>
+        <v>46° / 6+6</v>
       </c>
       <c r="F6" s="16">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C6*PI()/180)*Parameters!$C$9*(1+(D6-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.20000728121422151</v>
+        <f>Parameters!$C$9*(D6/Parameters!$C$8)/TAN((C6+Parameters!$C$7)*PI()/180)</f>
+        <v>0.2125683087136894</v>
       </c>
       <c r="G6" s="17">
         <f>F6*Parameters!$C$11</f>
-        <v>0.40001456242844302</v>
+        <v>0.4251366174273788</v>
       </c>
       <c r="H6" s="17">
-        <f t="shared" ref="H6:H11" si="1">G6/$G$6</f>
+        <f>G6/$G$6</f>
         <v>1</v>
       </c>
       <c r="I6" s="2"/>
@@ -3170,20 +3175,20 @@
         <v>6</v>
       </c>
       <c r="E7" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>C7&amp;"° / "&amp;D7&amp;"+"&amp;D7</f>
         <v>50° / 6+6</v>
       </c>
       <c r="F7" s="19">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C7*PI()/180)*Parameters!$C$9*(1+(D7-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.16782603589962378</v>
+        <f>Parameters!$C$9*(D7/Parameters!$C$8)/TAN((C7+Parameters!$C$7)*PI()/180)</f>
+        <v>0.1838044787800488</v>
       </c>
       <c r="G7" s="20">
         <f>F7*Parameters!$C$11</f>
-        <v>0.33565207179924755</v>
+        <v>0.3676089575600976</v>
       </c>
       <c r="H7" s="20">
-        <f t="shared" si="1"/>
-        <v>0.83909963117727993</v>
+        <f>G7/$G$6</f>
+        <v>0.8646842979195788</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -3195,27 +3200,27 @@
       </c>
       <c r="C8" s="15">
         <f>Parameters!C16</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="15">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
       <c r="E8" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>45° / 4+4</v>
+        <f>C8&amp;"° / "&amp;D8&amp;"+"&amp;D8</f>
+        <v>46° / 4+4</v>
       </c>
       <c r="F8" s="16">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C8*PI()/180)*Parameters!$C$9*(1+(D8-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.14093777329085042</v>
+        <f>Parameters!$C$9*(D8/Parameters!$C$8)/TAN((C8+Parameters!$C$7)*PI()/180)</f>
+        <v>0.14171220580912627</v>
       </c>
       <c r="G8" s="17">
         <f>F8*Parameters!$C$11</f>
-        <v>0.28187554658170083</v>
+        <v>0.28342441161825255</v>
       </c>
       <c r="H8" s="17">
-        <f t="shared" si="1"/>
-        <v>0.70466321243523333</v>
+        <f>G8/$G$6</f>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -3234,20 +3239,20 @@
         <v>4</v>
       </c>
       <c r="E9" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>C9&amp;"° / "&amp;D9&amp;"+"&amp;D9</f>
         <v>50° / 4+4</v>
       </c>
       <c r="F9" s="19">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C9*PI()/180)*Parameters!$C$9*(1+(D9-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.11826083358729966</v>
+        <f>Parameters!$C$9*(D9/Parameters!$C$8)/TAN((C9+Parameters!$C$7)*PI()/180)</f>
+        <v>0.12253631918669922</v>
       </c>
       <c r="G9" s="20">
         <f>F9*Parameters!$C$11</f>
-        <v>0.23652166717459933</v>
+        <v>0.24507263837339843</v>
       </c>
       <c r="H9" s="20">
-        <f t="shared" si="1"/>
-        <v>0.59128264165860145</v>
+        <f>G9/$G$6</f>
+        <v>0.5764561986130526</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -3266,20 +3271,20 @@
         <v>6</v>
       </c>
       <c r="E10" s="11" t="str">
-        <f t="shared" si="0"/>
+        <f>C10&amp;"° / "&amp;D10&amp;"+"&amp;D10</f>
         <v>62° / 6+6</v>
       </c>
       <c r="F10" s="16">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C10*PI()/180)*Parameters!$C$9*(1+(D10-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.10634575782257129</v>
+        <f>Parameters!$C$9*(D10/Parameters!$C$8)/TAN((C10+Parameters!$C$7)*PI()/180)</f>
+        <v>0.11142463925502127</v>
       </c>
       <c r="G10" s="17">
         <f>F10*Parameters!$C$11</f>
-        <v>0.21269151564514258</v>
+        <v>0.22284927851004255</v>
       </c>
       <c r="H10" s="17">
-        <f t="shared" si="1"/>
-        <v>0.53170943166147877</v>
+        <f>G10/$G$6</f>
+        <v>0.5241827435579796</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -3298,20 +3303,20 @@
         <v>4</v>
       </c>
       <c r="E11" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>C11&amp;"° / "&amp;D11&amp;"+"&amp;D11</f>
         <v>62° / 4+4</v>
       </c>
       <c r="F11" s="19">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C11*PI()/180)*Parameters!$C$9*(1+(D11-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>7.4937943336112409E-2</v>
+        <f>Parameters!$C$9*(D11/Parameters!$C$8)/TAN((C11+Parameters!$C$7)*PI()/180)</f>
+        <v>0.07428309283668086</v>
       </c>
       <c r="G11" s="20">
         <f>F11*Parameters!$C$11</f>
-        <v>0.14987588667222482</v>
+        <v>0.14856618567336172</v>
       </c>
       <c r="H11" s="20">
-        <f t="shared" si="1"/>
-        <v>0.37467607619668974</v>
+        <f>G11/$G$6</f>
+        <v>0.34945516237198637</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -3323,26 +3328,26 @@
       </c>
       <c r="C12" s="15">
         <f>Parameters!C19</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" s="15">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
       <c r="E12" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>38° / 6+6</v>
+        <f>C12&amp;"° / "&amp;D12&amp;"+"&amp;D12</f>
+        <v>40° / 6+6</v>
       </c>
       <c r="F12" s="16">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C12*PI()/180)*Parameters!$C$9*(1+(D12-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.25599764596783076</v>
+        <f>Parameters!$C$9*(D12/Parameters!$C$8)/TAN((C12+Parameters!$C$7)*PI()/180)</f>
+        <v>0.2625</v>
       </c>
       <c r="G12" s="17">
         <f>F12*Parameters!$C$11</f>
-        <v>0.51199529193566151</v>
+        <v>0.525</v>
       </c>
       <c r="H12" s="17">
-        <f t="shared" ref="H12:H17" si="2">G12/$G$12</f>
+        <f>G12/$G$12</f>
         <v>1</v>
       </c>
       <c r="I12" s="2"/>
@@ -3355,27 +3360,27 @@
       </c>
       <c r="C13" s="18">
         <f>Parameters!C20</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="18">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
       <c r="E13" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>45° / 6+6</v>
+        <f>C13&amp;"° / "&amp;D13&amp;"+"&amp;D13</f>
+        <v>46° / 6+6</v>
       </c>
       <c r="F13" s="19">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C13*PI()/180)*Parameters!$C$9*(1+(D13-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.20000728121422151</v>
+        <f>Parameters!$C$9*(D13/Parameters!$C$8)/TAN((C13+Parameters!$C$7)*PI()/180)</f>
+        <v>0.2125683087136894</v>
       </c>
       <c r="G13" s="20">
         <f>F13*Parameters!$C$11</f>
-        <v>0.40001456242844302</v>
+        <v>0.4251366174273788</v>
       </c>
       <c r="H13" s="20">
-        <f t="shared" si="2"/>
-        <v>0.78128562650671751</v>
+        <f>G13/$G$12</f>
+        <v>0.8097840331950072</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -3387,27 +3392,27 @@
       </c>
       <c r="C14" s="15">
         <f>Parameters!C19</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14" s="15">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
       <c r="E14" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>38° / 4+4</v>
+        <f>C14&amp;"° / "&amp;D14&amp;"+"&amp;D14</f>
+        <v>40° / 4+4</v>
       </c>
       <c r="F14" s="16">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C14*PI()/180)*Parameters!$C$9*(1+(D14-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.18039212358354917</v>
+        <f>Parameters!$C$9*(D14/Parameters!$C$8)/TAN((C14+Parameters!$C$7)*PI()/180)</f>
+        <v>0.17500000000000002</v>
       </c>
       <c r="G14" s="17">
         <f>F14*Parameters!$C$11</f>
-        <v>0.36078424716709834</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="H14" s="17">
-        <f t="shared" si="2"/>
-        <v>0.70466321243523333</v>
+        <f>G14/$G$12</f>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -3419,27 +3424,27 @@
       </c>
       <c r="C15" s="18">
         <f>Parameters!C21</f>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D15" s="18">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
       <c r="E15" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>50° / 6+6</v>
+        <f>C15&amp;"° / "&amp;D15&amp;"+"&amp;D15</f>
+        <v>54° / 6+6</v>
       </c>
       <c r="F15" s="19">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C15*PI()/180)*Parameters!$C$9*(1+(D15-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.16782603589962378</v>
+        <f>Parameters!$C$9*(D15/Parameters!$C$8)/TAN((C15+Parameters!$C$7)*PI()/180)</f>
+        <v>0.15772591249473464</v>
       </c>
       <c r="G15" s="20">
         <f>F15*Parameters!$C$11</f>
-        <v>0.33565207179924755</v>
+        <v>0.3154518249894693</v>
       </c>
       <c r="H15" s="20">
-        <f t="shared" si="2"/>
-        <v>0.65557648104589672</v>
+        <f>G15/$G$12</f>
+        <v>0.6008606190275605</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -3451,27 +3456,27 @@
       </c>
       <c r="C16" s="15">
         <f>Parameters!C20</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="15">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
       <c r="E16" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>45° / 4+4</v>
+        <f>C16&amp;"° / "&amp;D16&amp;"+"&amp;D16</f>
+        <v>46° / 4+4</v>
       </c>
       <c r="F16" s="16">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C16*PI()/180)*Parameters!$C$9*(1+(D16-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.14093777329085042</v>
+        <f>Parameters!$C$9*(D16/Parameters!$C$8)/TAN((C16+Parameters!$C$7)*PI()/180)</f>
+        <v>0.14171220580912627</v>
       </c>
       <c r="G16" s="17">
         <f>F16*Parameters!$C$11</f>
-        <v>0.28187554658170083</v>
+        <v>0.28342441161825255</v>
       </c>
       <c r="H16" s="17">
-        <f t="shared" si="2"/>
-        <v>0.55054323940369743</v>
+        <f>G16/$G$12</f>
+        <v>0.5398560221300048</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3483,27 +3488,27 @@
       </c>
       <c r="C17" s="18">
         <f>Parameters!C21</f>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D17" s="18">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
       <c r="E17" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>50° / 4+4</v>
+        <f>C17&amp;"° / "&amp;D17&amp;"+"&amp;D17</f>
+        <v>54° / 4+4</v>
       </c>
       <c r="F17" s="19">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C17*PI()/180)*Parameters!$C$9*(1+(D17-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.11826083358729966</v>
+        <f>Parameters!$C$9*(D17/Parameters!$C$8)/TAN((C17+Parameters!$C$7)*PI()/180)</f>
+        <v>0.1051506083298231</v>
       </c>
       <c r="G17" s="20">
         <f>F17*Parameters!$C$11</f>
-        <v>0.23652166717459933</v>
+        <v>0.2103012166596462</v>
       </c>
       <c r="H17" s="20">
-        <f t="shared" si="2"/>
-        <v>0.46196062913078734</v>
+        <f>G17/$G$12</f>
+        <v>0.4005737460183737</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3522,16 +3527,16 @@
         <v>6</v>
       </c>
       <c r="E18" s="11" t="str">
-        <f t="shared" si="0"/>
+        <f>C18&amp;"° / "&amp;D18&amp;"+"&amp;D18</f>
         <v>70° / 6+6</v>
       </c>
       <c r="F18" s="16">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C18*PI()/180)*Parameters!$C$9*(1+(D18-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>7.2796696998486426E-2</v>
+        <f>Parameters!$C$9*(D18/Parameters!$C$8)/TAN((C18+Parameters!$C$7)*PI()/180)</f>
+        <v>0.0703366630131697</v>
       </c>
       <c r="G18" s="17">
         <f>F18*Parameters!$C$11</f>
-        <v>0.14559339399697285</v>
+        <v>0.1406733260263394</v>
       </c>
       <c r="H18" s="17">
         <f>G18/$G$18</f>
@@ -3554,20 +3559,20 @@
         <v>4</v>
       </c>
       <c r="E19" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>C19&amp;"° / "&amp;D19&amp;"+"&amp;D19</f>
         <v>70° / 4+4</v>
       </c>
       <c r="F19" s="19">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C19*PI()/180)*Parameters!$C$9*(1+(D19-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>5.1297154361627746E-2</v>
+        <f>Parameters!$C$9*(D19/Parameters!$C$8)/TAN((C19+Parameters!$C$7)*PI()/180)</f>
+        <v>0.04689110867544646</v>
       </c>
       <c r="G19" s="20">
         <f>F19*Parameters!$C$11</f>
-        <v>0.10259430872325549</v>
+        <v>0.09378221735089293</v>
       </c>
       <c r="H19" s="20">
         <f>G19/$G$18</f>
-        <v>0.70466321243523322</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -3579,27 +3584,27 @@
       </c>
       <c r="C20" s="15">
         <f>Parameters!C23</f>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D20" s="15">
         <f>Parameters!G17</f>
         <v>6</v>
       </c>
       <c r="E20" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>85° / 6+6</v>
+        <f>C20&amp;"° / "&amp;D20&amp;"+"&amp;D20</f>
+        <v>80° / 6+6</v>
       </c>
       <c r="F20" s="16">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C20*PI()/180)*Parameters!$C$9*(1+(D20-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>1.7498369728885878E-2</v>
+        <f>Parameters!$C$9*(D20/Parameters!$C$8)/TAN((C20+Parameters!$C$7)*PI()/180)</f>
+        <v>0.022965774175555037</v>
       </c>
       <c r="G20" s="17">
         <f>F20*Parameters!$C$11</f>
-        <v>3.4996739457771757E-2</v>
+        <v>0.045931548351110074</v>
       </c>
       <c r="H20" s="17">
         <f>G20/$G$18</f>
-        <v>0.24037312749573927</v>
+        <v>0.3265121373650463</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -3611,35 +3616,37 @@
       </c>
       <c r="C21" s="18">
         <f>Parameters!C23</f>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D21" s="18">
         <f>Parameters!G16</f>
         <v>4</v>
       </c>
       <c r="E21" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>85° / 4+4</v>
+        <f>C21&amp;"° / "&amp;D21&amp;"+"&amp;D21</f>
+        <v>80° / 4+4</v>
       </c>
       <c r="F21" s="19">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C21*PI()/180)*Parameters!$C$9*(1+(D21-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>1.2330457425536163E-2</v>
+        <f>Parameters!$C$9*(D21/Parameters!$C$8)/TAN((C21+Parameters!$C$7)*PI()/180)</f>
+        <v>0.015310516117036693</v>
       </c>
       <c r="G21" s="20">
         <f>F21*Parameters!$C$11</f>
-        <v>2.4660914851072326E-2</v>
+        <v>0.030621032234073385</v>
       </c>
       <c r="H21" s="20">
         <f>G21/$G$18</f>
-        <v>0.16938210020425151</v>
+        <v>0.21767475824336424</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
-      <c r="B22" s="6" t="s">
-        <v>27</v>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Check 1</t>
+        </is>
       </c>
       <c r="C22" s="15">
         <f>Parameters!G8</f>
@@ -3650,16 +3657,16 @@
         <v>4</v>
       </c>
       <c r="E22" s="11" t="str">
-        <f t="shared" si="0"/>
+        <f>C22&amp;"° / "&amp;D22&amp;"+"&amp;D22</f>
         <v>40° / 4+4</v>
       </c>
       <c r="F22" s="16">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C22*PI()/180)*Parameters!$C$9*(1+(D22-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.16796309765159925</v>
+        <f>Parameters!$C$9*(D22/Parameters!$C$8)/TAN((C22+Parameters!$C$7)*PI()/180)</f>
+        <v>0.17500000000000002</v>
       </c>
       <c r="G22" s="17">
         <f>F22*Parameters!$C$11</f>
-        <v>0.3359261953031985</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="H22" s="17"/>
       <c r="I22" s="2"/>
@@ -3667,8 +3674,10 @@
     </row>
     <row r="23" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
-      <c r="B23" s="9" t="s">
-        <v>28</v>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Check 2</t>
+        </is>
       </c>
       <c r="C23" s="18">
         <f>Parameters!G9</f>
@@ -3679,16 +3688,16 @@
         <v>8</v>
       </c>
       <c r="E23" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f>C23&amp;"° / "&amp;D23&amp;"+"&amp;D23</f>
         <v>35° / 8+8</v>
       </c>
       <c r="F23" s="19">
-        <f>TAN(Parameters!$C$7*PI()/180)/TAN(C23*PI()/180)*Parameters!$C$9*(1+(D23-Parameters!$C$8)*Parameters!$C$10)</f>
-        <v>0.37</v>
+        <f>Parameters!$C$9*(D23/Parameters!$C$8)/TAN((C23+Parameters!$C$7)*PI()/180)</f>
+        <v>0.4171137574079735</v>
       </c>
       <c r="G23" s="20">
         <f>F23*Parameters!$C$11</f>
-        <v>0.74</v>
+        <v>0.834227514815947</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="2"/>

--- a/docs/diff_map.xlsx
+++ b/docs/diff_map.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99765EDB-0641-4162-AA91-CF6C903CC1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B34AEE-285A-433C-BAE6-8C1A6BA9DF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graph" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
   <si>
     <t>Astral · Differential parameters</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>保留的校核组合</t>
-  </si>
-  <si>
-    <t>参考 ramp 角度</t>
   </si>
   <si>
     <t>°</t>
@@ -67,16 +64,7 @@
     <t>n+n</t>
   </si>
   <si>
-    <t>原 Q5</t>
-  </si>
-  <si>
-    <t>参考游戏系数</t>
-  </si>
-  <si>
     <t>系数</t>
-  </si>
-  <si>
-    <t>每单位 n 修正</t>
   </si>
   <si>
     <t>百分比换算倍数</t>
@@ -118,17 +106,26 @@
     <t>相对参考组合</t>
   </si>
   <si>
-    <t>Check Q5</t>
+    <t>Astral · Differential map</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Reference Q6</t>
+    <t>Ramp 角度补偿</t>
   </si>
   <si>
-    <t>锚点 / 原 Q6</t>
+    <t>校核 1</t>
   </si>
   <si>
-    <t>Astral · Differential map</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>基础游戏系数</t>
+  </si>
+  <si>
+    <t>校核 2</t>
+  </si>
+  <si>
+    <t>Check 1</t>
+  </si>
+  <si>
+    <t>Check 2</t>
   </si>
 </sst>
 </file>
@@ -679,10 +676,19 @@
     <xf numFmtId="10" fontId="25" fillId="24" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -691,18 +697,9 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -720,7 +717,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -798,16 +795,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8646842979195788</c:v>
+                  <c:v>0.86468429791957879</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6666666666666667</c:v>
+                  <c:v>0.66666666666666674</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5764561986130526</c:v>
+                  <c:v>0.57645619861305264</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5241827435579796</c:v>
+                  <c:v>0.52418274355797956</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.34945516237198637</c:v>
@@ -964,7 +961,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -1042,16 +1039,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8097840331950072</c:v>
+                  <c:v>0.80978403319500725</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6666666666666667</c:v>
+                  <c:v>0.66666666666666674</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6008606190275605</c:v>
+                  <c:v>0.60086061902756049</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5398560221300048</c:v>
+                  <c:v>0.53985602213000483</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.4005737460183737</c:v>
@@ -1208,7 +1205,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -1280,10 +1277,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6666666666666666</c:v>
+                  <c:v>0.66666666666666663</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3265121373650463</c:v>
+                  <c:v>0.32651213736504631</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.21767475824336424</c:v>
@@ -1749,7 +1746,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:L54"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="4" width="10.5" customWidth="1"/>
@@ -1759,7 +1756,7 @@
     <col min="17" max="17" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1773,23 +1770,23 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
-      <c r="B2" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
+      <c r="B2" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1803,28 +1800,28 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
-      <c r="B5" s="25" t="str">
+      <c r="B5" s="24" t="str">
         <f>"Front power："&amp;Samples!E6&amp;" = 100%"</f>
         <v>Front power：46° / 6+6 = 100%</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1838,7 +1835,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1852,7 +1849,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1866,7 +1863,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1880,7 +1877,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1894,7 +1891,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1908,7 +1905,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1922,7 +1919,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1936,7 +1933,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1950,7 +1947,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1964,7 +1961,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1978,7 +1975,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1992,7 +1989,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2006,7 +2003,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2020,7 +2017,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2034,24 +2031,24 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
-      <c r="B21" s="25" t="str">
+      <c r="B21" s="24" t="str">
         <f>"Rear power："&amp;Samples!E12&amp;" = 100%"</f>
         <v>Rear power：40° / 6+6 = 100%</v>
       </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2065,7 +2062,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2079,7 +2076,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2093,7 +2090,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2107,7 +2104,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2121,7 +2118,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2135,7 +2132,7 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2149,7 +2146,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2163,7 +2160,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2177,7 +2174,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2191,7 +2188,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2205,7 +2202,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2219,7 +2216,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2233,7 +2230,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2247,7 +2244,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2261,24 +2258,24 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
-      <c r="B37" s="25" t="str">
+      <c r="B37" s="24" t="str">
         <f>"Coast："&amp;Samples!E18&amp;" = 100%"</f>
         <v>Coast：70° / 6+6 = 100%</v>
       </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="25"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2292,7 +2289,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2306,7 +2303,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2320,7 +2317,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2334,7 +2331,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2348,7 +2345,7 @@
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2362,7 +2359,7 @@
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2376,7 +2373,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2390,7 +2387,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2404,7 +2401,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2418,7 +2415,7 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2432,7 +2429,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2446,7 +2443,7 @@
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2460,7 +2457,7 @@
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
     </row>
-    <row r="51" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2474,7 +2471,7 @@
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
     </row>
-    <row r="52" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2488,7 +2485,7 @@
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
     </row>
-    <row r="53" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2502,7 +2499,7 @@
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
     </row>
-    <row r="54" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2535,7 +2532,7 @@
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -2547,7 +2544,7 @@
     <col min="9" max="12" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2561,23 +2558,23 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2591,11 +2588,11 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2609,68 +2606,64 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Ramp 角度补偿</t>
-        </is>
+      <c r="B7" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C7" s="5">
         <v>5</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>7</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="5">
         <v>8</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>校核 1</t>
-        </is>
+      <c r="F8" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G8" s="5">
         <v>40</v>
@@ -2683,24 +2676,20 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>基础游戏系数</t>
-        </is>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C9" s="10">
         <v>0.35</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>校核 2</t>
-        </is>
+      <c r="F9" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="G9" s="5">
         <v>35</v>
@@ -2713,10 +2702,10 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="8"/>
-      <c r="C10" s="27"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="8"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -2727,16 +2716,16 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" s="5">
         <v>2</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -2747,7 +2736,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2761,7 +2750,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2775,39 +2764,39 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
+      <c r="B14" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
+      <c r="F14" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2"/>
       <c r="F15" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -2815,10 +2804,10 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5">
         <v>46</v>
@@ -2838,10 +2827,10 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C17" s="5">
         <v>50</v>
@@ -2861,10 +2850,10 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C18" s="5">
         <v>62</v>
@@ -2879,10 +2868,10 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19" s="5">
         <v>40</v>
@@ -2891,10 +2880,10 @@
       <c r="E19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C20" s="5">
         <v>46</v>
@@ -2903,10 +2892,10 @@
       <c r="E20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C21" s="5">
         <v>54</v>
@@ -2915,10 +2904,10 @@
       <c r="E21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C22" s="5">
         <v>70</v>
@@ -2927,10 +2916,10 @@
       <c r="E22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C23" s="5">
         <v>80</v>
@@ -2945,7 +2934,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2959,43 +2948,43 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3009,7 +2998,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3051,7 +3040,7 @@
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3061,7 +3050,7 @@
     <col min="9" max="10" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3073,25 +3062,25 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
-      <c r="B2" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="B2" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3103,36 +3092,36 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" s="15">
         <f>Parameters!C16</f>
@@ -3143,7 +3132,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="11" t="str">
-        <f>C6&amp;"° / "&amp;D6&amp;"+"&amp;D6</f>
+        <f t="shared" ref="E6:E23" si="0">C6&amp;"° / "&amp;D6&amp;"+"&amp;D6</f>
         <v>46° / 6+6</v>
       </c>
       <c r="F6" s="16">
@@ -3152,19 +3141,19 @@
       </c>
       <c r="G6" s="17">
         <f>F6*Parameters!$C$11</f>
-        <v>0.4251366174273788</v>
+        <v>0.42513661742737879</v>
       </c>
       <c r="H6" s="17">
-        <f>G6/$G$6</f>
+        <f t="shared" ref="H6:H11" si="1">G6/$G$6</f>
         <v>1</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C7" s="18">
         <f>Parameters!C17</f>
@@ -3175,7 +3164,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="12" t="str">
-        <f>C7&amp;"° / "&amp;D7&amp;"+"&amp;D7</f>
+        <f t="shared" si="0"/>
         <v>50° / 6+6</v>
       </c>
       <c r="F7" s="19">
@@ -3184,19 +3173,19 @@
       </c>
       <c r="G7" s="20">
         <f>F7*Parameters!$C$11</f>
-        <v>0.3676089575600976</v>
+        <v>0.36760895756009759</v>
       </c>
       <c r="H7" s="20">
-        <f>G7/$G$6</f>
-        <v>0.8646842979195788</v>
+        <f t="shared" si="1"/>
+        <v>0.86468429791957879</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C8" s="15">
         <f>Parameters!C16</f>
@@ -3207,7 +3196,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="11" t="str">
-        <f>C8&amp;"° / "&amp;D8&amp;"+"&amp;D8</f>
+        <f t="shared" si="0"/>
         <v>46° / 4+4</v>
       </c>
       <c r="F8" s="16">
@@ -3219,16 +3208,16 @@
         <v>0.28342441161825255</v>
       </c>
       <c r="H8" s="17">
-        <f>G8/$G$6</f>
-        <v>0.6666666666666667</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666674</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" s="18">
         <f>Parameters!C17</f>
@@ -3239,7 +3228,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="12" t="str">
-        <f>C9&amp;"° / "&amp;D9&amp;"+"&amp;D9</f>
+        <f t="shared" si="0"/>
         <v>50° / 4+4</v>
       </c>
       <c r="F9" s="19">
@@ -3251,16 +3240,16 @@
         <v>0.24507263837339843</v>
       </c>
       <c r="H9" s="20">
-        <f>G9/$G$6</f>
-        <v>0.5764561986130526</v>
+        <f t="shared" si="1"/>
+        <v>0.57645619861305264</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C10" s="15">
         <f>Parameters!C18</f>
@@ -3271,7 +3260,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="11" t="str">
-        <f>C10&amp;"° / "&amp;D10&amp;"+"&amp;D10</f>
+        <f t="shared" si="0"/>
         <v>62° / 6+6</v>
       </c>
       <c r="F10" s="16">
@@ -3283,16 +3272,16 @@
         <v>0.22284927851004255</v>
       </c>
       <c r="H10" s="17">
-        <f>G10/$G$6</f>
-        <v>0.5241827435579796</v>
+        <f t="shared" si="1"/>
+        <v>0.52418274355797956</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C11" s="18">
         <f>Parameters!C18</f>
@@ -3303,28 +3292,28 @@
         <v>4</v>
       </c>
       <c r="E11" s="12" t="str">
-        <f>C11&amp;"° / "&amp;D11&amp;"+"&amp;D11</f>
+        <f t="shared" si="0"/>
         <v>62° / 4+4</v>
       </c>
       <c r="F11" s="19">
         <f>Parameters!$C$9*(D11/Parameters!$C$8)/TAN((C11+Parameters!$C$7)*PI()/180)</f>
-        <v>0.07428309283668086</v>
+        <v>7.4283092836680858E-2</v>
       </c>
       <c r="G11" s="20">
         <f>F11*Parameters!$C$11</f>
         <v>0.14856618567336172</v>
       </c>
       <c r="H11" s="20">
-        <f>G11/$G$6</f>
+        <f t="shared" si="1"/>
         <v>0.34945516237198637</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C12" s="15">
         <f>Parameters!C19</f>
@@ -3335,28 +3324,28 @@
         <v>6</v>
       </c>
       <c r="E12" s="11" t="str">
-        <f>C12&amp;"° / "&amp;D12&amp;"+"&amp;D12</f>
+        <f t="shared" si="0"/>
         <v>40° / 6+6</v>
       </c>
       <c r="F12" s="16">
         <f>Parameters!$C$9*(D12/Parameters!$C$8)/TAN((C12+Parameters!$C$7)*PI()/180)</f>
-        <v>0.2625</v>
+        <v>0.26250000000000001</v>
       </c>
       <c r="G12" s="17">
         <f>F12*Parameters!$C$11</f>
-        <v>0.525</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="H12" s="17">
-        <f>G12/$G$12</f>
+        <f t="shared" ref="H12:H17" si="2">G12/$G$12</f>
         <v>1</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" s="18">
         <f>Parameters!C20</f>
@@ -3367,7 +3356,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="12" t="str">
-        <f>C13&amp;"° / "&amp;D13&amp;"+"&amp;D13</f>
+        <f t="shared" si="0"/>
         <v>46° / 6+6</v>
       </c>
       <c r="F13" s="19">
@@ -3376,19 +3365,19 @@
       </c>
       <c r="G13" s="20">
         <f>F13*Parameters!$C$11</f>
-        <v>0.4251366174273788</v>
+        <v>0.42513661742737879</v>
       </c>
       <c r="H13" s="20">
-        <f>G13/$G$12</f>
-        <v>0.8097840331950072</v>
+        <f t="shared" si="2"/>
+        <v>0.80978403319500725</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C14" s="15">
         <f>Parameters!C19</f>
@@ -3399,7 +3388,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="11" t="str">
-        <f>C14&amp;"° / "&amp;D14&amp;"+"&amp;D14</f>
+        <f t="shared" si="0"/>
         <v>40° / 4+4</v>
       </c>
       <c r="F14" s="16">
@@ -3411,16 +3400,16 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H14" s="17">
-        <f>G14/$G$12</f>
-        <v>0.6666666666666667</v>
+        <f t="shared" si="2"/>
+        <v>0.66666666666666674</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C15" s="18">
         <f>Parameters!C21</f>
@@ -3431,7 +3420,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="12" t="str">
-        <f>C15&amp;"° / "&amp;D15&amp;"+"&amp;D15</f>
+        <f t="shared" si="0"/>
         <v>54° / 6+6</v>
       </c>
       <c r="F15" s="19">
@@ -3440,19 +3429,19 @@
       </c>
       <c r="G15" s="20">
         <f>F15*Parameters!$C$11</f>
-        <v>0.3154518249894693</v>
+        <v>0.31545182498946928</v>
       </c>
       <c r="H15" s="20">
-        <f>G15/$G$12</f>
-        <v>0.6008606190275605</v>
+        <f t="shared" si="2"/>
+        <v>0.60086061902756049</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C16" s="15">
         <f>Parameters!C20</f>
@@ -3463,7 +3452,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="11" t="str">
-        <f>C16&amp;"° / "&amp;D16&amp;"+"&amp;D16</f>
+        <f t="shared" si="0"/>
         <v>46° / 4+4</v>
       </c>
       <c r="F16" s="16">
@@ -3475,16 +3464,16 @@
         <v>0.28342441161825255</v>
       </c>
       <c r="H16" s="17">
-        <f>G16/$G$12</f>
-        <v>0.5398560221300048</v>
+        <f t="shared" si="2"/>
+        <v>0.53985602213000483</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C17" s="18">
         <f>Parameters!C21</f>
@@ -3495,28 +3484,28 @@
         <v>4</v>
       </c>
       <c r="E17" s="12" t="str">
-        <f>C17&amp;"° / "&amp;D17&amp;"+"&amp;D17</f>
+        <f t="shared" si="0"/>
         <v>54° / 4+4</v>
       </c>
       <c r="F17" s="19">
         <f>Parameters!$C$9*(D17/Parameters!$C$8)/TAN((C17+Parameters!$C$7)*PI()/180)</f>
-        <v>0.1051506083298231</v>
+        <v>0.10515060832982311</v>
       </c>
       <c r="G17" s="20">
         <f>F17*Parameters!$C$11</f>
-        <v>0.2103012166596462</v>
+        <v>0.21030121665964621</v>
       </c>
       <c r="H17" s="20">
-        <f>G17/$G$12</f>
+        <f t="shared" si="2"/>
         <v>0.4005737460183737</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C18" s="15">
         <f>Parameters!C22</f>
@@ -3527,16 +3516,16 @@
         <v>6</v>
       </c>
       <c r="E18" s="11" t="str">
-        <f>C18&amp;"° / "&amp;D18&amp;"+"&amp;D18</f>
+        <f t="shared" si="0"/>
         <v>70° / 6+6</v>
       </c>
       <c r="F18" s="16">
         <f>Parameters!$C$9*(D18/Parameters!$C$8)/TAN((C18+Parameters!$C$7)*PI()/180)</f>
-        <v>0.0703366630131697</v>
+        <v>7.0336663013169695E-2</v>
       </c>
       <c r="G18" s="17">
         <f>F18*Parameters!$C$11</f>
-        <v>0.1406733260263394</v>
+        <v>0.14067332602633939</v>
       </c>
       <c r="H18" s="17">
         <f>G18/$G$18</f>
@@ -3545,10 +3534,10 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C19" s="18">
         <f>Parameters!C22</f>
@@ -3559,28 +3548,28 @@
         <v>4</v>
       </c>
       <c r="E19" s="12" t="str">
-        <f>C19&amp;"° / "&amp;D19&amp;"+"&amp;D19</f>
+        <f t="shared" si="0"/>
         <v>70° / 4+4</v>
       </c>
       <c r="F19" s="19">
         <f>Parameters!$C$9*(D19/Parameters!$C$8)/TAN((C19+Parameters!$C$7)*PI()/180)</f>
-        <v>0.04689110867544646</v>
+        <v>4.6891108675446463E-2</v>
       </c>
       <c r="G19" s="20">
         <f>F19*Parameters!$C$11</f>
-        <v>0.09378221735089293</v>
+        <v>9.3782217350892927E-2</v>
       </c>
       <c r="H19" s="20">
         <f>G19/$G$18</f>
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C20" s="15">
         <f>Parameters!C23</f>
@@ -3591,28 +3580,28 @@
         <v>6</v>
       </c>
       <c r="E20" s="11" t="str">
-        <f>C20&amp;"° / "&amp;D20&amp;"+"&amp;D20</f>
+        <f t="shared" si="0"/>
         <v>80° / 6+6</v>
       </c>
       <c r="F20" s="16">
         <f>Parameters!$C$9*(D20/Parameters!$C$8)/TAN((C20+Parameters!$C$7)*PI()/180)</f>
-        <v>0.022965774175555037</v>
+        <v>2.2965774175555037E-2</v>
       </c>
       <c r="G20" s="17">
         <f>F20*Parameters!$C$11</f>
-        <v>0.045931548351110074</v>
+        <v>4.5931548351110074E-2</v>
       </c>
       <c r="H20" s="17">
         <f>G20/$G$18</f>
-        <v>0.3265121373650463</v>
+        <v>0.32651213736504631</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C21" s="18">
         <f>Parameters!C23</f>
@@ -3623,16 +3612,16 @@
         <v>4</v>
       </c>
       <c r="E21" s="12" t="str">
-        <f>C21&amp;"° / "&amp;D21&amp;"+"&amp;D21</f>
+        <f t="shared" si="0"/>
         <v>80° / 4+4</v>
       </c>
       <c r="F21" s="19">
         <f>Parameters!$C$9*(D21/Parameters!$C$8)/TAN((C21+Parameters!$C$7)*PI()/180)</f>
-        <v>0.015310516117036693</v>
+        <v>1.5310516117036693E-2</v>
       </c>
       <c r="G21" s="20">
         <f>F21*Parameters!$C$11</f>
-        <v>0.030621032234073385</v>
+        <v>3.0621032234073385E-2</v>
       </c>
       <c r="H21" s="20">
         <f>G21/$G$18</f>
@@ -3641,12 +3630,10 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Check 1</t>
-        </is>
+      <c r="B22" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C22" s="15">
         <f>Parameters!G8</f>
@@ -3657,7 +3644,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="11" t="str">
-        <f>C22&amp;"° / "&amp;D22&amp;"+"&amp;D22</f>
+        <f t="shared" si="0"/>
         <v>40° / 4+4</v>
       </c>
       <c r="F22" s="16">
@@ -3672,12 +3659,10 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Check 2</t>
-        </is>
+      <c r="B23" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="C23" s="18">
         <f>Parameters!G9</f>
@@ -3688,22 +3673,22 @@
         <v>8</v>
       </c>
       <c r="E23" s="12" t="str">
-        <f>C23&amp;"° / "&amp;D23&amp;"+"&amp;D23</f>
+        <f t="shared" si="0"/>
         <v>35° / 8+8</v>
       </c>
       <c r="F23" s="19">
         <f>Parameters!$C$9*(D23/Parameters!$C$8)/TAN((C23+Parameters!$C$7)*PI()/180)</f>
-        <v>0.4171137574079735</v>
+        <v>0.41711375740797352</v>
       </c>
       <c r="G23" s="20">
         <f>F23*Parameters!$C$11</f>
-        <v>0.834227514815947</v>
+        <v>0.83422751481594704</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3715,7 +3700,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3727,7 +3712,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:10" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>

--- a/docs/diff_map.xlsx
+++ b/docs/diff_map.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\xlsx-locale-20261027\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B34AEE-285A-433C-BAE6-8C1A6BA9DF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6463C25-4AC2-4668-823F-A9DBB6B75B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graph" sheetId="1" r:id="rId1"/>
     <sheet name="Parameters" sheetId="2" r:id="rId2"/>
-    <sheet name="Samples" sheetId="3" r:id="rId3"/>
+    <sheet name="Locale" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="Samples" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
   <si>
     <t>Astral · Differential parameters</t>
   </si>
@@ -73,9 +74,6 @@
     <t>倍</t>
   </si>
   <si>
-    <t>Ramp 角度</t>
-  </si>
-  <si>
     <t>摩擦面数量</t>
   </si>
   <si>
@@ -106,26 +104,245 @@
     <t>相对参考组合</t>
   </si>
   <si>
+    <t>校核 1</t>
+  </si>
+  <si>
+    <t>基础游戏系数</t>
+  </si>
+  <si>
+    <t>校核 2</t>
+  </si>
+  <si>
+    <t>Check 1</t>
+  </si>
+  <si>
+    <t>Check 2</t>
+  </si>
+  <si>
+    <t>Language / 语言</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>en-US</t>
+  </si>
+  <si>
+    <t>zh-CN</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>chart.seriesOne</t>
+  </si>
+  <si>
+    <t>Series 1</t>
+  </si>
+  <si>
+    <t>系列 1</t>
+  </si>
+  <si>
+    <t>label.angleDeg</t>
+  </si>
+  <si>
+    <t>Angle (°)</t>
+  </si>
+  <si>
+    <t>label.application</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>label.baseGameCoefficient</t>
+  </si>
+  <si>
+    <t>Base game coefficient</t>
+  </si>
+  <si>
+    <t>label.checkOne</t>
+  </si>
+  <si>
+    <t>label.checkTwo</t>
+  </si>
+  <si>
+    <t>label.coast</t>
+  </si>
+  <si>
+    <t>滑行</t>
+  </si>
+  <si>
+    <t>label.coastPrefix</t>
+  </si>
+  <si>
+    <t>Coast:</t>
+  </si>
+  <si>
+    <t>滑行：</t>
+  </si>
+  <si>
+    <t>label.coefficient</t>
+  </si>
+  <si>
+    <t>Coefficient</t>
+  </si>
+  <si>
+    <t>label.combination</t>
+  </si>
+  <si>
+    <t>Combination</t>
+  </si>
+  <si>
+    <t>label.facesPerSide</t>
+  </si>
+  <si>
+    <t>n per side</t>
+  </si>
+  <si>
+    <t>label.frictionFaces</t>
+  </si>
+  <si>
+    <t>Friction faces</t>
+  </si>
+  <si>
+    <t>label.frontPower</t>
+  </si>
+  <si>
+    <t>前轴驱动</t>
+  </si>
+  <si>
+    <t>label.frontPowerPrefix</t>
+  </si>
+  <si>
+    <t>Front power:</t>
+  </si>
+  <si>
+    <t>前轴驱动：</t>
+  </si>
+  <si>
+    <t>label.gameCoefficientC</t>
+  </si>
+  <si>
+    <t>Game coefficient c</t>
+  </si>
+  <si>
+    <t>label.modelEquivalentPercentage</t>
+  </si>
+  <si>
+    <t>Model equivalent percentage</t>
+  </si>
+  <si>
+    <t>label.modelReference</t>
+  </si>
+  <si>
+    <t>Model reference</t>
+  </si>
+  <si>
+    <t>label.percentageMultiplier</t>
+  </si>
+  <si>
+    <t>Percentage conversion multiplier</t>
+  </si>
+  <si>
+    <t>label.rampAngle</t>
+  </si>
+  <si>
+    <t>Ramp angle</t>
+  </si>
+  <si>
+    <t>坡角</t>
+  </si>
+  <si>
+    <t>label.rampAngleCompensation</t>
+  </si>
+  <si>
+    <t>Ramp angle compensation</t>
+  </si>
+  <si>
+    <t>坡角补偿</t>
+  </si>
+  <si>
+    <t>label.rampDeg</t>
+  </si>
+  <si>
+    <t>坡角 (°)</t>
+  </si>
+  <si>
+    <t>label.rearPowerRamp</t>
+  </si>
+  <si>
+    <t>后轴驱动</t>
+  </si>
+  <si>
+    <t>label.rearPowerRampColon</t>
+  </si>
+  <si>
+    <t>Rear power:</t>
+  </si>
+  <si>
+    <t>后轴驱动：</t>
+  </si>
+  <si>
+    <t>label.referenceFacesPerSide</t>
+  </si>
+  <si>
+    <t>Reference n per side</t>
+  </si>
+  <si>
+    <t>label.relativeReferenceCombination</t>
+  </si>
+  <si>
+    <t>Relative reference combination</t>
+  </si>
+  <si>
+    <t>label.relativeToReference</t>
+  </si>
+  <si>
+    <t>Relative to reference</t>
+  </si>
+  <si>
+    <t>相对参考值</t>
+  </si>
+  <si>
+    <t>label.retainedCheckCombinations</t>
+  </si>
+  <si>
+    <t>Retained check combinations</t>
+  </si>
+  <si>
+    <t>label.times</t>
+  </si>
+  <si>
+    <t>times</t>
+  </si>
+  <si>
+    <t>title.differentialMap</t>
+  </si>
+  <si>
     <t>Astral · Differential map</t>
+  </si>
+  <si>
+    <t>Astral · 差速器曲线</t>
+  </si>
+  <si>
+    <t>title.differentialParameters</t>
+  </si>
+  <si>
+    <t>Astral · 差速器参数</t>
+  </si>
+  <si>
+    <t>title.differentialSamples</t>
+  </si>
+  <si>
+    <t>Astral · 差速器采样</t>
+  </si>
+  <si>
+    <t>简体中文</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ramp 角度补偿</t>
-  </si>
-  <si>
-    <t>校核 1</t>
-  </si>
-  <si>
-    <t>基础游戏系数</t>
-  </si>
-  <si>
-    <t>校核 2</t>
-  </si>
-  <si>
-    <t>Check 1</t>
-  </si>
-  <si>
-    <t>Check 2</t>
   </si>
 </sst>
 </file>
@@ -136,7 +353,7 @@
     <numFmt numFmtId="176" formatCode="0.0000"/>
     <numFmt numFmtId="177" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,8 +523,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,8 +659,21 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -606,13 +849,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -679,6 +929,8 @@
     <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -687,6 +939,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -699,7 +957,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -717,28 +975,37 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1125">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>Front power</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$14</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>前轴驱动</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1125">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -751,7 +1018,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Series 1</c:v>
+            <c:strRef>
+              <c:f>Locale!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>系列 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -867,7 +1142,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -901,18 +1176,27 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Relative to reference</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>相对参考值</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US"/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -925,7 +1209,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -961,28 +1245,37 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1125">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>Rear power</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$23</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>后轴驱动</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1125">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -995,7 +1288,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Series 1</c:v>
+            <c:strRef>
+              <c:f>Locale!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>系列 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1111,7 +1412,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -1145,18 +1446,27 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Relative to reference</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>相对参考值</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US"/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -1169,7 +1479,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -1205,28 +1515,37 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1125">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>Coast</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$8</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>滑行</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1125">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1239,7 +1558,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Series 1</c:v>
+            <c:strRef>
+              <c:f>Locale!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>系列 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1343,7 +1670,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -1377,18 +1704,27 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Relative to reference</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>相对参考值</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US"/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -1401,7 +1737,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -1429,7 +1765,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -1741,12 +2077,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFEE2300-6DFF-4BA3-966C-9197F55A2948}">
   <sheetPr>
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:L54"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="4" width="10.5" customWidth="1"/>
@@ -1756,7 +2092,816 @@
     <col min="17" max="17" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="24" t="str">
+        <f>VLOOKUP("title.differentialMap",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>Astral · 差速器曲线</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="26" t="str">
+        <f>VLOOKUP("label.frontPowerPrefix",Locale!$A$2:$D$32,4,FALSE)&amp;Samples!E6&amp;" = 100%"</f>
+        <v>前轴驱动：46° / 6+6 = 100%</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="26" t="str">
+        <f>VLOOKUP("label.rearPowerRampColon",Locale!$A$2:$D$32,4,FALSE)&amp;Samples!E12&amp;" = 100%"</f>
+        <v>后轴驱动：40° / 6+6 = 100%</v>
+      </c>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="26" t="str">
+        <f>VLOOKUP("label.coastPrefix",Locale!$A$2:$D$32,4,FALSE)&amp;Samples!E18&amp;" = 100%"</f>
+        <v>滑行：70° / 6+6 = 100%</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+    </row>
+    <row r="46" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="B37:K37"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="E1:G1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"English,简体中文"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2365027D-F440-4572-BE21-249CF241A928}">
+  <sheetPr>
+    <tabColor rgb="FFC49A32"/>
+  </sheetPr>
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="8" width="12" customWidth="1"/>
+    <col min="9" max="12" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1770,23 +2915,24 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
+      <c r="B2" s="29" t="str">
+        <f>VLOOKUP("title.differentialParameters",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>Astral · 差速器参数</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1800,88 +2946,136 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="24" t="str">
-        <f>"Front power："&amp;Samples!E6&amp;" = 100%"</f>
-        <v>Front power：46° / 6+6 = 100%</v>
-      </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="30" t="str">
+        <f>VLOOKUP("label.modelReference",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>模型基准</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="F6" s="30" t="str">
+        <f>VLOOKUP("label.retainedCheckCombinations",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>保留的校核组合</v>
+      </c>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="B7" s="4" t="str">
+        <f>VLOOKUP("label.rampAngleCompensation",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>坡角补偿</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="F7" s="7" t="str">
+        <f>VLOOKUP("label.combination",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>组合</v>
+      </c>
+      <c r="G7" s="7" t="str">
+        <f>VLOOKUP("label.angleDeg",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>角度 (°)</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <f>VLOOKUP("label.facesPerSide",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>单侧 n</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="8" t="str">
+        <f>VLOOKUP("label.referenceFacesPerSide",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>参考单侧 n</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="F8" s="4" t="str">
+        <f>VLOOKUP("label.checkOne",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>校核 1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>40</v>
+      </c>
+      <c r="H8" s="5">
+        <v>4</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="B9" s="4" t="str">
+        <f>VLOOKUP("label.baseGameCoefficient",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>基础游戏系数</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="D9" s="4" t="str">
+        <f>VLOOKUP("label.coefficient",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>系数</v>
+      </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="F9" s="8" t="str">
+        <f>VLOOKUP("label.checkTwo",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>校核 2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>35</v>
+      </c>
+      <c r="H9" s="5">
+        <v>8</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -1891,11 +3085,19 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="B11" s="4" t="str">
+        <f>VLOOKUP("label.percentageMultiplier",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>百分比换算倍数</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4" t="str">
+        <f>VLOOKUP("label.times",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>倍</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1905,7 +3107,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1919,7 +3121,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1933,66 +3135,109 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="B14" s="30" t="str">
+        <f>VLOOKUP("label.rampAngle",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>坡角</v>
+      </c>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="F14" s="30" t="str">
+        <f>VLOOKUP("label.frictionFaces",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>摩擦面数量</v>
+      </c>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="B15" s="7" t="str">
+        <f>VLOOKUP("label.application",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>用途</v>
+      </c>
+      <c r="C15" s="7" t="str">
+        <f>VLOOKUP("label.angleDeg",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>角度 (°)</v>
+      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="F15" s="7" t="str">
+        <f>VLOOKUP("label.combination",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>组合</v>
+      </c>
+      <c r="G15" s="7" t="str">
+        <f>VLOOKUP("label.facesPerSide",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>单侧 n</v>
+      </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="6" t="str">
+        <f>VLOOKUP("label.frontPower",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>前轴驱动</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46</v>
+      </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="F16" s="11" t="str">
+        <f>G16&amp;"+"&amp;G16</f>
+        <v>4+4</v>
+      </c>
+      <c r="G16" s="5">
+        <v>4</v>
+      </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="9" t="str">
+        <f>VLOOKUP("label.frontPower",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>前轴驱动</v>
+      </c>
+      <c r="C17" s="5">
+        <v>50</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="F17" s="12" t="str">
+        <f>G17&amp;"+"&amp;G17</f>
+        <v>6+6</v>
+      </c>
+      <c r="G17" s="5">
+        <v>6</v>
+      </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="6" t="str">
+        <f>VLOOKUP("label.frontPower",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>前轴驱动</v>
+      </c>
+      <c r="C18" s="5">
+        <v>62</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -2003,69 +3248,67 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="9" t="str">
+        <f>VLOOKUP("label.rearPowerRamp",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>后轴驱动</v>
+      </c>
+      <c r="C19" s="5">
+        <v>40</v>
+      </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="6" t="str">
+        <f>VLOOKUP("label.rearPowerRamp",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>后轴驱动</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
-      <c r="B21" s="24" t="str">
-        <f>"Rear power："&amp;Samples!E12&amp;" = 100%"</f>
-        <v>Rear power：40° / 6+6 = 100%</v>
-      </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
+      <c r="B21" s="9" t="str">
+        <f>VLOOKUP("label.rearPowerRamp",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>后轴驱动</v>
+      </c>
+      <c r="C21" s="5">
+        <v>54</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="B22" s="6" t="str">
+        <f>VLOOKUP("label.coast",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>滑行</v>
+      </c>
+      <c r="C22" s="5">
+        <v>70</v>
+      </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="B23" s="9" t="str">
+        <f>VLOOKUP("label.coast",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>滑行</v>
+      </c>
+      <c r="C23" s="5">
+        <v>80</v>
+      </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -2076,7 +3319,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2090,133 +3333,43 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2230,775 +3383,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
-      <c r="B37" s="24" t="str">
-        <f>"Coast："&amp;Samples!E18&amp;" = 100%"</f>
-        <v>Coast：70° / 6+6 = 100%</v>
-      </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-    </row>
-    <row r="41" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-    </row>
-    <row r="42" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="47" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-    </row>
-    <row r="48" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-    </row>
-    <row r="49" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-    </row>
-    <row r="50" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-    </row>
-    <row r="51" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-    </row>
-    <row r="52" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-    </row>
-    <row r="53" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-    </row>
-    <row r="54" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="B21:K21"/>
-    <mergeCell ref="B37:K37"/>
-  </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFC49A32"/>
-  </sheetPr>
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="12" width="10.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="5">
-        <v>5</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="5">
-        <v>8</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="5">
-        <v>40</v>
-      </c>
-      <c r="H8" s="5">
-        <v>4</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="10">
-        <v>0.35</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="5">
-        <v>35</v>
-      </c>
-      <c r="H9" s="5">
-        <v>8</v>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="5">
-        <v>46</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="11" t="str">
-        <f>G16&amp;"+"&amp;G16</f>
-        <v>4+4</v>
-      </c>
-      <c r="G16" s="5">
-        <v>4</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="5">
-        <v>50</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="12" t="str">
-        <f>G17&amp;"+"&amp;G17</f>
-        <v>6+6</v>
-      </c>
-      <c r="G17" s="5">
-        <v>6</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="5">
-        <v>62</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="5">
-        <v>40</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="5">
-        <v>46</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="5">
-        <v>54</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="5">
-        <v>70</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="5">
-        <v>80</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3031,16 +3416,507 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B2E8A0-7B57-4146-9944-43DC3482081E}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B2,C2)</f>
+        <v>系列 1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B3,C3)</f>
+        <v>角度 (°)</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B4,C4)</f>
+        <v>用途</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B5,C5)</f>
+        <v>基础游戏系数</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B6,C6)</f>
+        <v>校核 1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B7,C7)</f>
+        <v>校核 2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B8,C8)</f>
+        <v>滑行</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B9,C9)</f>
+        <v>滑行：</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B10,C10)</f>
+        <v>系数</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B11,C11)</f>
+        <v>组合</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B12,C12)</f>
+        <v>单侧 n</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B13,C13)</f>
+        <v>摩擦面数量</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B14,C14)</f>
+        <v>前轴驱动</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B15,C15)</f>
+        <v>前轴驱动：</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B16,C16)</f>
+        <v>游戏系数 c</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B17,C17)</f>
+        <v>模型等效百分比</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B18,C18)</f>
+        <v>模型基准</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B19,C19)</f>
+        <v>百分比换算倍数</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B20,C20)</f>
+        <v>坡角</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B21,C21)</f>
+        <v>坡角补偿</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B22,C22)</f>
+        <v>坡角 (°)</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B23,C23)</f>
+        <v>后轴驱动</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B24,C24)</f>
+        <v>后轴驱动：</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B25,C25)</f>
+        <v>参考单侧 n</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B26,C26)</f>
+        <v>相对参考组合</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B27,C27)</f>
+        <v>相对参考值</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B28,C28)</f>
+        <v>保留的校核组合</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B29,C29)</f>
+        <v>倍</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B30,C30)</f>
+        <v>Astral · 差速器曲线</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B31,C31)</f>
+        <v>Astral · 差速器参数</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D32" s="22" t="str">
+        <f>IF(Graph!$E$1="English",B32,C32)</f>
+        <v>Astral · 差速器采样</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2906CE-3304-46DB-BE4D-4CA2B1175CEC}">
   <sheetPr>
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3050,7 +3926,7 @@
     <col min="9" max="10" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3062,25 +3938,26 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="35.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
+      <c r="B2" s="29" t="str">
+        <f>VLOOKUP("title.differentialSamples",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>Astral · 差速器采样</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3092,36 +3969,44 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="32.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>22</v>
+      <c r="B5" s="13" t="str">
+        <f>VLOOKUP("label.application",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>用途</v>
+      </c>
+      <c r="C5" s="14" t="str">
+        <f>VLOOKUP("label.rampDeg",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>坡角 (°)</v>
+      </c>
+      <c r="D5" s="13" t="str">
+        <f>VLOOKUP("label.facesPerSide",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>单侧 n</v>
+      </c>
+      <c r="E5" s="13" t="str">
+        <f>VLOOKUP("label.combination",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>组合</v>
+      </c>
+      <c r="F5" s="13" t="str">
+        <f>VLOOKUP("label.gameCoefficientC",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>游戏系数 c</v>
+      </c>
+      <c r="G5" s="13" t="str">
+        <f>VLOOKUP("label.modelEquivalentPercentage",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>模型等效百分比</v>
+      </c>
+      <c r="H5" s="13" t="str">
+        <f>VLOOKUP("label.relativeReferenceCombination",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>相对参考组合</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="6" t="s">
-        <v>15</v>
+      <c r="B6" s="6" t="str">
+        <f>VLOOKUP("label.frontPower",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>前轴驱动</v>
       </c>
       <c r="C6" s="15">
         <f>Parameters!C16</f>
@@ -3150,10 +4035,11 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="9" t="s">
-        <v>15</v>
+      <c r="B7" s="9" t="str">
+        <f>VLOOKUP("label.frontPower",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>前轴驱动</v>
       </c>
       <c r="C7" s="18">
         <f>Parameters!C17</f>
@@ -3182,10 +4068,11 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="6" t="s">
-        <v>15</v>
+      <c r="B8" s="6" t="str">
+        <f>VLOOKUP("label.frontPower",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>前轴驱动</v>
       </c>
       <c r="C8" s="15">
         <f>Parameters!C16</f>
@@ -3214,10 +4101,11 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="9" t="s">
-        <v>15</v>
+      <c r="B9" s="9" t="str">
+        <f>VLOOKUP("label.frontPower",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>前轴驱动</v>
       </c>
       <c r="C9" s="18">
         <f>Parameters!C17</f>
@@ -3246,10 +4134,11 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="6" t="s">
-        <v>15</v>
+      <c r="B10" s="6" t="str">
+        <f>VLOOKUP("label.frontPower",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>前轴驱动</v>
       </c>
       <c r="C10" s="15">
         <f>Parameters!C18</f>
@@ -3278,10 +4167,11 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="9" t="s">
-        <v>15</v>
+      <c r="B11" s="9" t="str">
+        <f>VLOOKUP("label.frontPower",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>前轴驱动</v>
       </c>
       <c r="C11" s="18">
         <f>Parameters!C18</f>
@@ -3310,10 +4200,11 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="6" t="s">
-        <v>16</v>
+      <c r="B12" s="6" t="str">
+        <f>VLOOKUP("label.rearPowerRamp",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>后轴驱动</v>
       </c>
       <c r="C12" s="15">
         <f>Parameters!C19</f>
@@ -3342,10 +4233,11 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
-      <c r="B13" s="9" t="s">
-        <v>16</v>
+      <c r="B13" s="9" t="str">
+        <f>VLOOKUP("label.rearPowerRamp",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>后轴驱动</v>
       </c>
       <c r="C13" s="18">
         <f>Parameters!C20</f>
@@ -3374,10 +4266,11 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="6" t="s">
-        <v>16</v>
+      <c r="B14" s="6" t="str">
+        <f>VLOOKUP("label.rearPowerRamp",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>后轴驱动</v>
       </c>
       <c r="C14" s="15">
         <f>Parameters!C19</f>
@@ -3406,10 +4299,11 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="9" t="s">
-        <v>16</v>
+      <c r="B15" s="9" t="str">
+        <f>VLOOKUP("label.rearPowerRamp",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>后轴驱动</v>
       </c>
       <c r="C15" s="18">
         <f>Parameters!C21</f>
@@ -3438,10 +4332,11 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="6" t="s">
-        <v>16</v>
+      <c r="B16" s="6" t="str">
+        <f>VLOOKUP("label.rearPowerRamp",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>后轴驱动</v>
       </c>
       <c r="C16" s="15">
         <f>Parameters!C20</f>
@@ -3470,10 +4365,11 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="B17" s="9" t="s">
-        <v>16</v>
+      <c r="B17" s="9" t="str">
+        <f>VLOOKUP("label.rearPowerRamp",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>后轴驱动</v>
       </c>
       <c r="C17" s="18">
         <f>Parameters!C21</f>
@@ -3502,10 +4398,11 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="6" t="s">
-        <v>17</v>
+      <c r="B18" s="6" t="str">
+        <f>VLOOKUP("label.coast",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>滑行</v>
       </c>
       <c r="C18" s="15">
         <f>Parameters!C22</f>
@@ -3534,10 +4431,11 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="9" t="s">
-        <v>17</v>
+      <c r="B19" s="9" t="str">
+        <f>VLOOKUP("label.coast",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>滑行</v>
       </c>
       <c r="C19" s="18">
         <f>Parameters!C22</f>
@@ -3566,10 +4464,11 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="6" t="s">
-        <v>17</v>
+      <c r="B20" s="6" t="str">
+        <f>VLOOKUP("label.coast",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>滑行</v>
       </c>
       <c r="C20" s="15">
         <f>Parameters!C23</f>
@@ -3598,10 +4497,11 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
-      <c r="B21" s="9" t="s">
-        <v>17</v>
+      <c r="B21" s="9" t="str">
+        <f>VLOOKUP("label.coast",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>滑行</v>
       </c>
       <c r="C21" s="18">
         <f>Parameters!C23</f>
@@ -3630,10 +4530,11 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
-      <c r="B22" s="6" t="s">
-        <v>28</v>
+      <c r="B22" s="6" t="str">
+        <f>VLOOKUP("label.checkOne",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>校核 1</v>
       </c>
       <c r="C22" s="15">
         <f>Parameters!G8</f>
@@ -3659,10 +4560,11 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="1:10" ht="30.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="31" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
-      <c r="B23" s="9" t="s">
-        <v>29</v>
+      <c r="B23" s="9" t="str">
+        <f>VLOOKUP("label.checkTwo",Locale!$A$2:$D$32,4,FALSE)</f>
+        <v>校核 2</v>
       </c>
       <c r="C23" s="18">
         <f>Parameters!G9</f>
@@ -3688,7 +4590,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3700,7 +4602,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3712,7 +4614,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="23.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3730,5 +4632,6 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>